--- a/backend/rag_evaluation_report.xlsx
+++ b/backend/rag_evaluation_report.xlsx
@@ -455,7 +455,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>生成时间：2026-04-20 09:57:16</t>
+          <t>生成时间：2026-04-21 11:55:36</t>
         </is>
       </c>
     </row>
@@ -498,14 +498,14 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.575</v>
+        <v>0.762</v>
       </c>
       <c r="C6" t="n">
-        <v>0.513</v>
+        <v>0.68</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.062</t>
+          <t>-0.082</t>
         </is>
       </c>
     </row>
@@ -516,14 +516,14 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.503</v>
+        <v>0.658</v>
       </c>
       <c r="C7" t="n">
-        <v>0.608</v>
+        <v>0.733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>+0.105</t>
+          <t>+0.075</t>
         </is>
       </c>
     </row>
@@ -534,14 +534,14 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.536</v>
+        <v>0.706</v>
       </c>
       <c r="C8" t="n">
-        <v>0.556</v>
+        <v>0.705</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>+0.020</t>
+          <t>-0.001</t>
         </is>
       </c>
     </row>
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="13">
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.85</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="14">
@@ -597,7 +597,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+0.35</t>
+          <t>+0.45</t>
         </is>
       </c>
     </row>
@@ -681,13 +681,13 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E2" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0.667</v>
+        <v>0.833</v>
       </c>
       <c r="G2" s="4" t="n">
         <v>1</v>
@@ -717,7 +717,7 @@
         <v>0.75</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0.667</v>
+        <v>0.833</v>
       </c>
       <c r="G3" s="4" t="n">
         <v>0.75</v>
@@ -751,7 +751,7 @@
         <v>0.75</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>0.8</v>
+        <v>0.571</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>0.75</v>
@@ -779,20 +779,20 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F5" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="E5" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>0.429</v>
-      </c>
       <c r="G5" s="4" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>根腐病、排水</t>
+          <t>排水</t>
         </is>
       </c>
     </row>
@@ -813,20 +813,20 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="4" t="n">
         <v>0.75</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>0.5</v>
-      </c>
       <c r="F6" s="4" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>嫩梢、啶虫脒</t>
+          <t>啶虫脒</t>
         </is>
       </c>
     </row>
@@ -850,17 +850,17 @@
         <v>0.75</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.429</v>
+        <v>0.667</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>红蜘蛛、螨类</t>
+          <t>螨类</t>
         </is>
       </c>
     </row>
@@ -881,20 +881,20 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>介壳虫、蚧壳虫、矿物油、若虫</t>
+          <t>蚧壳虫</t>
         </is>
       </c>
     </row>
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E9" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="E9" s="4" t="n">
-        <v>0.75</v>
-      </c>
       <c r="F9" s="4" t="n">
-        <v>0.4</v>
+        <v>0.667</v>
       </c>
       <c r="G9" s="4" t="n">
         <v>0.75</v>
@@ -949,13 +949,13 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>0.2</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.25</v>
+        <v>0.667</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>0.2</v>
@@ -983,22 +983,18 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>缺钙、裂果、石灰、钙肥</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1023,7 +1019,7 @@
         <v>0.4</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.25</v>
+        <v>0.429</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>0.4</v>
@@ -1051,13 +1047,13 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.286</v>
+        <v>0.714</v>
       </c>
       <c r="G13" s="4" t="n">
         <v>0.75</v>
@@ -1085,13 +1081,13 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>0.75</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
       <c r="G14" s="4" t="n">
         <v>0.75</v>
@@ -1125,7 +1121,7 @@
         <v>0.75</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.429</v>
+        <v>0.286</v>
       </c>
       <c r="G15" s="4" t="n">
         <v>0.75</v>
@@ -1153,13 +1149,13 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="4" t="n">
         <v>0.75</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>0.625</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>1</v>
@@ -1183,13 +1179,13 @@
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.8</v>
+        <v>0.857</v>
       </c>
       <c r="G17" s="4" t="n">
         <v>0.8</v>
@@ -1217,13 +1213,13 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G18" s="4" t="n">
         <v>0.5</v>
@@ -1251,13 +1247,13 @@
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>0.75</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="G19" s="4" t="n">
         <v>0.75</v>
@@ -1288,17 +1284,17 @@
         <v>1</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="F20" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>朋娜、果实特征</t>
+          <t>果实特征</t>
         </is>
       </c>
     </row>
@@ -1319,18 +1315,22 @@
         </is>
       </c>
       <c r="D21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="G21" s="4" t="n">
         <v>0.75</v>
       </c>
-      <c r="E21" s="4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="4" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>熏烟</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1419,44 +1419,42 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
+          <t>脐橙黄龙病的症状主要包括以下几点：
+1. **叶片症状**：
+   - 叶片出现黄化斑驳。
+   - 出现花叶、小叶现象。
+   - 有时会出现“绿岛”现象，即叶片上出现绿色的小斑块。
+2. **果实症状**：
+   - 果实可能出现“青果”或“红鼻果”现象，即果实颜色不均匀，部分区域呈现绿色或红色。
+3. **根系及土壤微生态变化**：
+   - 患病植株的根系吸水吸肥能力受损。
+   - 根际土壤中部分有益菌减少，而部分致病菌属（如镰刀菌属和曲霉属）增加。
+   - 根际全氮、全磷含量下降，说明黄龙病不仅影响树体，也扰动了土壤微生物群落。
+这些症状表明黄龙病对脐橙树体及其生长环境有显著的影响。</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
           <t>根据提供的参考资料，脐橙黄龙病的症状主要包括：
 1. **叶片症状**：
    - 叶片出现黄化斑驳。
    - 出现花叶现象。
-   - 产生小叶。
-   - 形成“绿岛”（即在黄化的叶片上出现绿色的小区域）。
+   - 产生小叶或“绿岛”现象。
 2. **果实症状**：
-   - 果实可能出现“青果”或“红鼻果”的情况。“青果”指的是果实成熟时仍保持绿色；“红鼻果”则指果实顶部呈现红色而其余部分未正常着色的现象。
+   - 果实可能出现“青果”或“红鼻果”。
 3. **根系及土壤微生态变化**：
    - 植株根系吸水吸肥能力受损。
-   - 根际土壤中部分有益菌减少，而镰刀菌属和曲霉属等致病相关菌属增加。
-   - 全氮、全磷含量下降，这不仅影响了树体健康，也对土壤微生物群落造成了扰动。
-4. **其他症状**：
-   - 韧皮部坏死、筛管堵塞，导致营养物质运输受阻。
-   - 显著降低产量和品质。
-以上信息综合了资料中的描述，展示了黄龙病对脐橙植株从地上部分到地下部分的全面影响。</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>根据提供的参考资料，脐橙黄龙病的症状主要包括以下几点：
-1. **叶片症状**：
-   - 叶片出现黄化斑驳、花叶（即叶片颜色不均匀）、小叶。
-   - 出现“绿岛”现象，即在黄色的叶片上出现绿色的小斑块。
-2. **果实症状**：
-   - 果实可能出现“青果”或“红鼻果”的情况。“青果”指的是果实成熟时仍保持青色；“红鼻果”则是指果实顶部呈现红色而其余部分未正常着色。
-3. **根系及土壤微生态变化**：
-   - 患病植株的根系吸水吸肥能力受损，导致韧皮部坏死、筛管堵塞。
-   - 根际土壤中部分有益菌减少，而镰刀菌属和曲霉属等致病相关菌属增加。
-   - 土壤中的全氮、全磷含量下降，这表明黄龙病不仅影响树体健康，还对土壤微生物群落产生负面影响。
-以上信息综合了资料1至资料3中关于黄龙病症状的具体描述。</t>
+   - 韧皮部坏死、筛管堵塞。
+   - 根际土壤中部分有益菌减少，而部分致病菌属（如镰刀菌属和曲霉属）增加。
+   - 全氮、全磷含量下降，影响微生物群落结构。
+这些症状表明黄龙病不仅对脐橙树体造成直接损害，还会影响其生长环境中的土壤微生物平衡。</t>
         </is>
       </c>
       <c r="H2" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -1482,58 +1480,68 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>根据提供的参考资料，脐橙溃疡病的防治方法主要包括以下几个方面：
-1. **治虫控病**：
-   - 严格控制潜叶蛾的数量，因为它们是溃疡病菌的主要携带者和传播者。
-   - 推广使用性信息素诱控技术来减少害虫数量。
-   - 在成虫活动低峰期统一放梢，以减少新梢被感染的机会。
-   - 根据实际情况适时喷洒农药保护新梢免受侵害。
-2. **关键施药时期（基于道县气候条件）**：
-   - 春梢：4月15日至20日进行第一次施药。
-   - 夏梢：5月25日至30日开始首次施药。
-   - 秋梢：8月10日至15日实施初次处理。
-   - 果实溃疡病预防：5月15日至20日启动首轮治疗。
-   - 每次施药后大约每隔10天视具体情况再追加1至2次施药。
-   - 台风或暴雨前后也应采取措施施药保护果树。
-   - 整个生长周期内通常需要进行6到9次的防治工作。
-3. **推荐使用的药物**：
-   - 包括噻唑锌、松脂酸铜、氢氧化铜等在内的多种铜基制剂。
-   - 建议将有机铜制剂与其他类型的杀菌剂混合使用，并且定期更换不同作用机制的药品以延缓抗药性的产生。
-   - 对于农用抗生素如链霉素等，由于国家对其管理越来越严格，因此建议谨慎使用。
-   - 在果实快速膨大阶段（7月至采收前），尤其是在高温条件下，应该限制铜基产品的应用。
-4. **防虫网技术的应用**：
-   - 使用60目的防虫网覆盖可以有效降低潜叶蛾及其他害虫对果园的影响。
-   - 此外，这种做法还能减轻强降雨及强风对树木造成的损害，从而间接降低了溃疡病的发生率。
-请注意，上述信息主要针对特定地区的气候条件给出了一些建议。实际操作时还需结合当地的具体情况进行调整。</t>
+          <t>根据提供的参考资料，柑橘溃疡病的防治措施主要包括以下几个方面：
+1. **预防为主，综合防治**：
+   - 以农业和物理防治为基础，生物防治为核心。
+   - 根据病虫害发生规律和经济阈值确定化学防治时机。
+2. **关键施药时期（道县气候）**：
+   - 春梢：4月15～20日施第1次药
+   - 夏梢：5月25～30日施第1次药
+   - 秋梢：8月10～15日施第1次药
+   - 果实溃疡病：5月15～20日施第1次药
+   - 每次施药后相隔10天根据情况再施1～2次；台风暴雨前及大风大雨后施药保护
+   - 全年防治6～9次（春梢1～2次，夏梢2～3次，秋梢2次，保果2～3次）
+3. **推荐药剂**：
+   - 噻唑锌、松脂酸铜、氢氧化铜、硫酸铜钙、噻菌铜、中生·乙酸铜、春雷·王铜、春雷霉素等
+   - 推荐有机铜制剂与其他杀菌剂混配，交替轮换使用延缓抗药性
+   - 农用抗生素（链霉素等）国家管控趋严，建议慎用
+   - 果实膨大后期（7月至采收前，高温季节）控制使用铜制剂
+4. **治虫控病**：
+   - 严格防治潜叶蛾（携带传播溃疡病菌）
+   - 推广性信息素诱控技术
+   - 成虫低峰期统一放梢
+   - 适时喷药保梢
+5. **防虫网技术**：
+   - 使用60目防虫网覆盖，减少潜叶蛾等害虫危害，减弱暴雨大风对果树冲击，降低溃疡病发病率
+6. **防控策略**：
+   - 新梢长至2cm时及谢花后幼果期，喷施氢氧化铜、噻唑锌等铜制剂
+   - 严格防治潜叶蛾，切断病菌侵染的伤口来源
+通过上述措施，可以有效控制柑橘溃疡病的发生和蔓延。需要注意的是，在选择农药时应避免使用烈性农药和未登记农药，并且要合理轮换使用不同作用机理的药剂，以延缓抗药性的产生。</t>
         </is>
       </c>
       <c r="F3" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>根据提供的参考资料，脐橙溃疡病的防治措施主要包括以下几个方面：
-1. **治虫控病**：
-   - 严格控制潜叶蛾（因为它们可以携带并传播溃疡病菌）。
-   - 推广使用性信息素诱控技术来减少害虫数量。
-   - 在成虫活动低峰期统一放梢，以减少新梢受到侵害的机会。
-   - 根据实际情况适时喷洒农药保护新梢。
-2. **关键施药时期**（基于道县气候条件）：
-   - 春梢：4月15日至20日进行第一次施药。
-   - 夏梢：5月25日至30日开始首次施药。
-   - 秋梢：8月10日至15日实施初次处理。
-   - 果实溃疡病预防：5月15日至20日启动首轮治疗。
-   - 每次施药后大约10天视具体情况决定是否需要再次施药1至2次。
-   - 台风暴雨前后也应采取相应措施保护植株免受损害。
-   - 整个生长周期内通常需要进行6到9次防治工作（春梢1-2次、夏梢2-3次、秋梢2次、保果阶段2-3次）。
-3. **推荐使用的药剂**：
-   - 包括噻唑锌、松脂酸铜、氢氧化铜、硫酸铜钙、噻菌铜、中生·乙酸铜、春雷·王铜以及春雷霉素等。
-   - 建议将有机铜制剂与其他类型的杀菌剂混合使用，并且定期更换不同作用机制的产品以延缓抗药性的产生。
-   - 对于农用抗生素如链霉素等，由于国家政策趋于严格管理，因此在使用时需谨慎考虑。
-   - 高温季节特别是从7月至采收前这段时间内，应该限制铜基产品的应用频率。
-4. **防虫网技术的应用**：
-   - 使用60目规格的防虫网覆盖果园，这不仅可以有效降低潜叶蛾等害虫的危害程度，还能减轻强降雨和大风对果树造成的物理损伤，从而间接减少了溃疡病的发生率。
-综上所述，通过综合运用上述方法，可以有效地管理和控制脐橙溃疡病。请注意，在实际操作过程中还需结合当地具体情况进行适当调整。</t>
+          <t>根据提供的参考资料，柑橘溃疡病的防治措施主要包括以下几个方面：
+1. **预防为主，综合防治**：
+   - 以农业和物理防治为基础，生物防治为核心。
+   - 化学防治作为补充手段，不应使用烈性农药和未登记农药。
+2. **治虫控病**：
+   - 严格防治潜叶蛾（携带传播溃疡病菌）。
+   - 推广性信息素诱控技术。
+   - 成虫低峰期统一放梢。
+   - 适时喷药保梢。
+3. **关键施药时期**（以道县气候为例）：
+   - 春梢：4月15～20日施第1次药。
+   - 夏梢：5月25～30日施第1次药。
+   - 秋梢：8月10～15日施第1次药。
+   - 果实溃疡病：5月15～20日施第1次药。
+   - 每次施药后相隔10天根据情况再施1～2次。
+   - 台风暴雨前及大风大雨后施药保护。
+   - 全年防治6～9次（春梢1～2次，夏梢2～3次，秋梢2次，保果2～3次）。
+4. **推荐药剂**：
+   - 噻唑锌、松脂酸铜、氢氧化铜、硫酸铜钙、噻菌铜、中生·乙酸铜、春雷·王铜、春雷霉素等。
+   - 推荐有机铜制剂与其他杀菌剂混配，交替轮换使用延缓抗药性。
+   - 农用抗生素（如链霉素）国家管控趋严，建议慎用。
+   - 果实膨大后期（7月至采收前，高温季节）控制使用铜制剂。
+5. **防虫网技术**：
+   - 使用60目防虫网覆盖，减少潜叶蛾等害虫危害，减弱暴雨大风对果树冲击，降低溃疡病发病率。
+6. **其他防控策略**：
+   - 新梢长至2cm时及谢花后幼果期，喷施氢氧化铜、噻唑锌等铜制剂。
+   - 严格防治潜叶蛾，切断病菌侵染的伤口来源。
+以上是基于现有资料整理出的柑橘溃疡病防治方法。请注意，具体操作还需结合当地实际情况进行调整。</t>
         </is>
       </c>
       <c r="H3" s="4" t="n">
@@ -1563,18 +1571,21 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>根据提供的参考资料，对于脐橙炭疽病的防治方法如下：
-- **药剂防治**：
-  - 可以使用70%甲基托布津800倍液或10%世高水分散剂6,000倍液进行喷洒。
-  - 在果实着色期间，建议连续喷洒2至3次45%咪鲜胺1,000～1,500倍液。
-  - 对于往年果实发病较重的果园，应在果实在转色期开始时就开始喷药。
-- **非化学措施**：
-  - 加强栽培管理，增强树势，提高植株自身的抵抗力。
-  - 注意防寒防冻，减少因低温造成的伤害，从而降低病害发生的机会。
-  - 及时防治其他病虫害，保持果园的整体健康状态。
-- **预防性措施**：
-  - 资料指出，赣南早脐橙虽然对溃疡病有一定耐受力，但容易感染枯枝型炭疽病。因此，在每年的3月至5月（该病的高发期），应每隔10到15天喷一次杀菌剂作为预防措施。
-请注意，除了上述直接针对炭疽病的方法外，还推荐采取更加综合性的绿色防控策略来管理整个果园的健康状况，比如优化树体结构、改善通风透光条件等，这些都有助于减少包括炭疽病在内的多种病虫害的发生。</t>
+          <t>脐橙炭疽病的治疗主要包括以下几个方面：
+1. **症状识别**：
+   - **果实**：初期果面出现黑色针尖状小斑，后扩大为黑褐色、略微凸起的圆形斑块，环境潮湿时斑点上会出现橙红色粘质小点。
+   - **叶片与枝干**：导致叶片干枯脱落、枝条枯死，严重时引发大量落果。
+2. **防治药剂**：
+   - **治疗性喷雾**：可以使用70%甲基托布津800倍液或10%世高（苯醚甲环唑）水分散剂6,000倍液进行喷施。对于往年果实发病较重的果园，在果实转色期开始喷药，并且在果实着色期连续喷洒2～3次45%咪鲜胺1,000～1,500倍液。
+   - **清园处理**：冬季及早春期间，使用石硫合剂对整个果园进行全面喷施，以消灭越冬病原菌，减少初始侵染源。
+3. **关键防治期**：
+   - **雨季前**：重点预防叶片和枝梢感病。
+   - **采收前**：重点预防果实蒂腐病，确保贮藏期品质。
+   - 对于赣南早脐橙而言，3月至5月是炭疽病的高发期，建议每10至15天喷一次杀菌剂。
+4. **其他管理措施**：
+   - 加强栽培管理，增强树势。
+   - 防寒防冻，及时防治其他病虫害，特别是要注意同步控制可能造成伤口的害虫如潜叶蛾等，因为这些伤口容易成为病菌入侵的途径。
+以上就是关于脐橙炭疽病的主要治疗方法，请根据实际情况选择合适的防治策略。</t>
         </is>
       </c>
       <c r="F4" s="4" t="n">
@@ -1582,18 +1593,23 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>根据提供的参考资料，脐橙炭疽病的防治措施如下：
-1. **药剂防治**：
-   - 使用70%甲基托布津800倍液或10%世高水分散剂6,000倍液进行喷洒。
-   - 在果实着色期连续喷施2～3次45%咪鲜胺1,000～1,500倍液。
-2. **预防性喷药**：
-   - 对于往年果实发病较重的果园，在果实在转色期开始喷药。
-   - 一般情况下，3月至5月为炭疽病的高发期，建议每10～15天喷一次杀菌剂以预防疾病发生。
-3. **加强栽培管理**：
-   - 增强树势，提高植株自身抵抗能力。
-   - 注意防寒防冻，减少因低温造成的伤害。
-   - 及时防治其他病虫害，避免交叉感染或加重病情。
-请注意，虽然上述方法可以有效控制炭疽病的发生和发展，但在实际操作过程中还需要结合当地具体情况灵活调整。同时，提倡采用绿色防控策略，比如通过改善果园环境、合理修剪等非化学手段来降低病害风险。</t>
+          <t>脐橙炭疽病的治疗和预防措施如下：
+1. **症状识别**：
+   - **果实**：初期果面出现黑色针尖状小斑，后扩大为黑褐色、略微凸起的圆形斑块，环境潮湿时斑点上会出现橙红色粘质小点。
+   - **叶片与枝干**：导致叶片干枯脱落、枝条枯死，严重时引发大量落果。
+2. **防治药剂**：
+   - **治疗性喷雾**：
+     - 使用70%甲基托布津800倍液
+     - 或使用10%世高（苯醚甲环唑）水分散剂6,000倍液
+   - **清园处理**：冬季及早春使用石硫合剂进行全园喷施，以消灭越冬病原菌，减少初始侵染源。
+3. **关键防治期**：
+   - **雨季前**：重点预防叶片和枝梢感病。
+   - **采收前**：重点预防果实蒂腐病，确保贮藏期品质。
+4. **其他管理措施**：
+   - 加强栽培管理，增强树势，防寒防冻，及时防治其他病虫害。
+   - 往年果实发病较重的果园，果实在转色期开始喷药。
+   - 果实着色期连喷2～3次45%咪鲜胺1,000～1,500倍液。
+通过上述措施可以有效控制脐橙炭疽病的发生和蔓延。</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
@@ -1623,7 +1639,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>知识库中没有找到关于脐橙根腐病的具体原因和处理方法的信息。根据提供的参考资料，主要讨论了脐橙种植过程中的一些其他方面，如土壤健康、特定病虫害（如炭疽病、黄龙病）的防治措施等，但未直接提及根腐病的相关内容。如果需要了解根腐病的原因及处理办法，建议查阅更专门针对该问题的资料或咨询农业专家。</t>
+          <t>知识库中没有找到关于脐橙根腐病的具体原因和处理方法的信息。提供的参考资料主要讨论了脐橙的其他几种病害，如树脂病/流胶病、炭疽病以及黄龙病等，并未提及根腐病的相关内容。如果需要了解根腐病的信息，建议查阅专门针对该病害的研究资料或咨询农业专家。</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
@@ -1631,11 +1647,33 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>知识库中没有找到关于脐橙根腐病的具体原因和处理方法的信息。对于脐橙的其他病害如黄龙病、炭疽病等有较为详细的描述，但未特别提及根腐病的相关内容。如果需要了解这些已知病害的信息或其他种植管理建议，请告知！</t>
+          <t>根据提供的参考资料，关于脐橙根腐病的原因和处理方法如下：
+### 诱发原因
+- **果园积水**：导致根系长期缺氧。
+- **土壤过酸或连作**：这会导致有害微生物积累。
+- **机械损伤**：中耕施肥时可能对根系造成伤害。
+- **使用未腐熟有机肥**：这种肥料可能会烧伤根部。
+### 处理步骤
+1. **急救处理**：
+   - 扒开根部周围的土壤以晾晒根部，通过光照通风来抑制病菌生长。
+2. **药剂灌根**：
+   - 可选用以下几种药剂之一进行灌根处理：
+     - **甲霜·锰锌**：稀释至500～800倍液，特别适用于控制疫霉菌。
+     - **多菌灵/甲基硫菌灵**：稀释至600倍液，具有广谱杀菌效果。
+     - **铜高尚/硫酸铜**：按照产品说明书指示配比使用，提供较强的保护作用。
+3. **促根复壮**：
+   - 灌施含有腐植酸的生根剂。
+   - 增加施用已经充分腐熟的有机肥料。
+   - 使用枯草芽孢杆菌等有益微生物改善土壤环境。
+### 预防措施
+- 实行深沟高畦种植方式，确保雨后不会积水。
+- 施用的所有有机肥料必须经过充分腐熟后再使用。
+- 春秋两季定期检查果园状况，做到早发现、早处理。
+- 对于已知患病树木处理完毕后，所有工具都需要彻底消毒，防止病害扩散。</t>
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -1661,19 +1699,35 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>根据提供的参考资料，柑橘木虱的防治措施主要包括以下几个方面：
-1. **统一放梢**：通过统一时间让果树发新梢，可以缩短木虱的危害期，减少其繁殖和传播的机会。
-2. **清除寄主植物**：移除果园周围的九里香等可能作为木虱寄主的植物，以减少木虱的数量及其迁移至脐橙树上的可能性。
-3. **营造防护林**：在果园周围种植防护林带，利用树木形成自然屏障来阻止或减缓木虱从外部迁入果园内。
-4. **化学防治**：
-   - 当新梢长到约2厘米时进行首次喷药处理（推荐使用噻虫嗪加高效氯氰菊酯）。
-   - 之后每隔7天左右再补充一次喷药。
-   - 在果实收获后也应对整个果园进行全面清理并施用农药，以消灭残留的木虱。
-5. **黄板诱杀**：设置黄色粘虫板吸引并捕捉木虱。建议每亩地放置20至30张黄板。
-6. **病树处置**：
-   - 对于已经感染了黄龙病的树木，在砍伐前1至3天需要对全园进行彻底喷药，防止带有病菌的木虱逃逸到健康的树木上。
-   - 砍掉病树后，对于留下的树桩采取“十字划涂草甘膦+覆膜”的方法处理，防止其再生长出新的枝条成为木虱的新宿主。
-以上就是关于柑橘木虱的主要防控策略。请注意，实际操作时还需结合当地具体情况灵活调整，并遵循相关农业技术指导原则。</t>
+          <t>柑橘木虱的防治可以采取综合措施，包括生态隔离、农业防治、物理防治、生物防治以及化学防治等方法。具体如下：
+### 1. 生态隔离
+- 将果园划分为13～20公顷的种植单元。
+- 单元之间设置宽度超过10米、树高至少7米的防护林带。
+- 在山顶保留带帽林，在山脊上保留乔木隔离带。
+### 2. 农业防治
+- **统一放梢**：6月中旬前控制零星嫩梢生长，之后统一放出夏梢；8月上旬前统一放出秋梢；9月下旬后及时控制晚秋梢的生长。
+- **清除寄主植物**：清理果园周边可能成为柑橘木虱寄主的植物，如枳壳、黄皮和九里香等。
+### 3. 物理防治
+- 使用无病毒苗木，并在60目网室内假植1至2年后再进行定植（对于黄龙病高发区建议全程采用60目网室栽培）。
+- 悬挂带有性引诱剂的黄色粘板，高度距离地面约150厘米，每4到5米放置一块，主要挂在南侧方向，每亩地使用20至30张。
+### 4. 生物防治
+- 实行生草栽培以保护天敌昆虫，如寄生蜂、瓢虫、草蛉和其他捕食性昆虫。
+- 当柑橘木虱处于2至3龄若虫阶段时释放亮腹釉小蜂或柑橘木虱啮小蜂。
+- 在空气湿度达到或超过70%的情况下，在发生区域释放白僵菌（浓度为1×10⁸孢子/mL）。
+- 于每年2月中下旬，在柑橘园四周及行间套种2至4行烟草（第一行与橘树的距离应小于1米）。
+### 5. 化学防治
+- **施药时机**：
+  - 春梢长至0.5～2厘米、夏梢长至0.5～1厘米、秋梢长至0.5～1厘米时根据实际情况决定是否需要喷药。
+  - 每次新梢期可用药1至3次，每隔7至10天施用一次。
+  - 冬季采果后及春芽萌动前各喷洒一次药物。
+- **根部施药**（适用于未挂果的幼树）：
+  - 选择低毒且内吸性强、持效期较长的农药。
+  - 施药时间应在春梢和秋梢萌发前一周进行，每年不超过两次。
+  - 土壤田间持水量需保持在60%～80%，如果低于60%，则先对表层土壤（深度约20厘米）进行湿润处理。
+  - 根据树木不同生长阶段调整施药量：幼树2.5～5升/株；初结果树6～10升/株；盛果树15～20升/株。
+  - 安全间隔期要求最后一次根施距果实采收不少于80天。
+  - 可通过滴灌（流速≤2升/小时）、微喷（流速3～5升/小时）或者直接浇灌的方式给药。
+以上就是关于柑橘木虱防治的主要措施，请根据具体情况灵活应用。</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
@@ -1681,27 +1735,36 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>柑橘木虱的防治可以从以下几个方面进行：
-1. **化学防治**：
-   - 新梢长至2厘米时首次喷药，推荐使用噻虫嗪加高效氯氰菊酯的组合。7天后需要再次补喷。
-   - 采果后进行全面清园处理。
-2. **物理防治**：
-   - 使用黄板诱杀技术，每667平方米放置20-30张黄板来吸引并捕捉木虱。
-3. **农业措施**：
-   - 统一放梢以缩短木虱的危害期。
-   - 清除果园周围的九里香等可能作为木虱寄主的植物。
-   - 营造防护林带，利用自然屏障减少木虱从外部迁入果园的机会。
-4. **病树管理**：
-   - 发现感染黄龙病的树木必须立即砍除，并在砍伐前1-3天对整个果园喷洒农药，防止带有病菌的木虱逃逸到健康的树木上。
-   - 对于被砍掉的树桩，采用“十字划涂草甘膦+覆膜”的方法处理，可以有效防止其再生新芽。
-5. **根部施药（适用于幼树）**：
-   - 施用内吸性强、低毒且持效期较长的农药。
-   - 施药时间选择在春梢和秋梢萌发前一周，每年不超过两次。
-   - 土壤含水量应保持在田间持水量的60%～80%，如果低于60%，则需先喷水湿润表层土壤（深度约20厘米）。
-   - 根据不同生长阶段调整施药剂量：幼树2.5～5升/株；初结果树6～10升/株；盛果树15～20升/株。
-   - 注意最后一次根部施药与果实采摘之间至少间隔80天。
-   - 可通过滴灌（流速≤2升/小时）、微喷（流速3～5升/小时）或直接浇灌的方式进行施药。
-以上就是关于柑橘木虱防治的主要策略，请根据实际情况灵活应用。</t>
+          <t>柑橘木虱的防治可以采取综合措施，包括生态隔离、农业防治、物理防治、生物防治和化学防治等方法。具体如下：
+### 1. 生态隔离
+- 将果园划分为13～20公顷的种植单元。
+- 单元间设置宽度超过10米、树高不低于7米的防护林。
+- 山顶保留带帽林，山脊处保留乔木隔离带。
+### 2. 农业防治
+- **统一放梢**：控制零星嫩梢的生长，在6月中旬前清除零星夏梢后统一放出夏梢；8月上旬前统一放出秋梢；9月下旬后出现的晚秋梢应及时控除。
+- **清除寄主植物**：移除果园周边可能成为柑橘木虱寄主的植物，如枳壳、黄皮、九里香等。
+### 3. 物理防治
+- 使用无病毒苗木，并在60目或以上网室内假植1至2年后再定植（对于黄龙病高发区，建议全程采用60目网室栽培）。
+- 在果园四周及园内悬挂带有性引诱剂的黄色粘板，高度距离地面约150厘米，每4到5米放置一块，主要挂在南侧方向。
+### 4. 生物防治
+- 实行生草栽培以保护天敌（例如寄生蜂、瓢虫、草蛉和其他捕食性昆虫）。
+- 当柑橘木虱处于2～3龄若虫阶段时，释放亮腹釉小蜂或柑橘木虱啮小蜂。
+- 当空气湿度达到或超过70%时，在发生区域释放白僵菌（浓度为1×10⁸孢子/mL）。
+- 于每年2月中下旬，在柑橘园周围及行间套种2至4行烟草（第一行与橘树的距离应小于1米）。
+### 5. 化学防治
+- **施药时机**：
+  - 春梢长至0.5～2厘米、夏梢长至0.5～1厘米、秋梢长至0.5～1厘米时根据害虫情况决定是否需要喷药；每隔7～10天喷一次药，每个新梢期总共喷1～3次。
+  - 冬季防治：采果后以及春芽开始萌动之前各喷一次药。
+  - 同一区域内应在两天内完成全部喷药工作；同时对地面及周围的杂草进行处理以防止木虱逃避。
+  - 台风过后需立即检查果园状况，一旦发现成虫活动即刻喷洒农药。
+- **根部施药**（适用于未挂果的幼树）：
+  - 选择低毒、内吸性强且持效期较长的农药。
+  - 施药时间点为春梢和秋梢萌发前一周，每年不超过两次。
+  - 土壤含水量应保持在田间持水量的60%～80%，如果低于60%，则先通过喷水使表层土壤湿润（深度约20厘米）。
+  - 根据树木的不同生长阶段调整施药剂量：幼树2.5～5升/株；初结果树6～10升/株；盛果树15～20升/株。
+  - 安全间隔期要求最后一次根部施药与果实采摘之间至少相隔80天。
+  - 可采用滴灌（流速≤2 L/h）、微喷（流速3～5 L/h）或者直接浇灌的方式给药。
+以上就是关于柑橘木虱防治的主要措施。希望这些信息能够帮助您有效地管理您的果园。</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
@@ -1731,45 +1794,44 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>根据提供的参考资料，提到的螨类害虫主要是柑橘全爪螨（也称作红蜘蛛），但没有直接提供针对红蜘蛛的具体防治措施。不过，可以参考关于柑橘全爪螨和其他类似害螨的管理建议来处理红蜘蛛问题：
-1. **轮换使用不同作用机制的药剂**：长期单一用药容易导致害螨产生抗药性，因此需要定期更换不同类型的杀螨剂，避免连续使用同一种药物。
-2. **绿色防控策略**：
-   - 监测预警：定期检查果园内害螨的发生情况。
-   - 合理修剪：通过修剪改善树冠内的通风透光条件，减少害螨滋生环境。
-   - 清园工作：清除落叶、枯枝等可能成为害螨越冬场所的物质。
-   - 生草抑尘：适当保留地面植被有助于抑制灰尘飞扬，同时为天敌提供栖息地。
-   - 保护天敌：鼓励自然天敌如捕食螨的存在，以生物控制方式降低害螨数量。
-   - 精准施药：仅在必要时进行化学防治，并确保准确覆盖目标区域。
-3. **推荐使用的药剂**：虽然资料中未明确列出用于红蜘蛛的具体药剂，但提到了一些可用于柑橘全爪螨的药剂，如阿维菌素、哒螨灵、乙螨唑和螺螨酯等。这些药剂也可能对红蜘蛛有效，但在实际应用前最好咨询当地农业技术推广部门或专业人士确认适用性和剂量。
-请注意，上述信息基于现有资料整理而成，对于特定条件下红蜘蛛的最佳防治方法，请结合实际情况并参考专业意见执行。如果遇到严重爆发或其他特殊情况，建议联系相关专家获取更详细的指导。</t>
+          <t>针对红蜘蛛（橘全爪螨）对脐橙的危害，可以采取以下措施进行防治：
+1. **了解发生规律**：
+   - 红蜘蛛一年内可发生12～15代。
+   - 春梢期（3月左右）和高温干旱期（7～8月）是其暴发高峰期。
+2. **监测与防治指标**：
+   - 当平均每片叶子上的红蜘蛛数量达到或超过2头时，应开始用药防治。
+3. **化学防治方法**：
+   - 第一次施药建议使用乙唑螨腈加上阿维菌素，这两种药物组合能有效杀灭成螨及若螨。
+   - 七天之后，再用苯肼酯等药物处理，以消灭若螨和卵。
+   - 喷洒时要特别注意喷到叶片背面以及枝条之间的缝隙处，并确保喷透。
+4. **抗药性管理**：
+   - 赣南地区已发现某些红蜘蛛种群对阿维菌素、哒螨灵、乙螨唑、螺螨酯产生了抗药性。
+   - 因此，在实际操作中应该建立轮换用药机制，避免长时间单一使用同一种药剂。
+5. **生物防治**：
+   - 推广使用尼氏钝绥螨、胡瓜钝绥螨等天敌来控制红蜘蛛的数量。
+   - 通过果园生草等方式保护这些有益昆虫，提高自然控制效果。
+综上所述，对于红蜘蛛的防控需要结合化学手段与生物方法，并且要注意合理安排用药策略，防止害虫产生抗药性。同时也要注重改善果园生态环境，增强植物自身的抵抗力。</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>根据提供的参考资料，红蜘蛛并不是直接提到的害虫名称，但柑橘全爪螨和锈壁虱（也称为锈蜘蛛）是脐橙园中常见的螨类害虫。这里假设您所指的“红蜘蛛”可能是其中的一种。基于此，我将提供关于这两种螨类害虫的防治方法。
-### 柑橘全爪螨
-- **抗药性管理**：长期单一用药易产生抗药性，建议轮换使用不同作用机制的药剂，避免连续使用同类杀螨剂。
-- **绿色防控思路**：包括监测预警、合理修剪以改善小气候条件、清园、生草抑尘、保护天敌以及精准施药等措施。
-### 锈壁虱（锈蜘蛛）
-- **危害**：刺吸果实与叶片汁液，导致果面形成黑褐色网状斑点，降低商品价值。
-- **早期监测**：从5月份开始，使用10倍放大镜检查叶背及果面，当每片叶子上发现≥2头时即需要采取防治措施。
-- **防治关键期**：
-  - 第一阶段：5月下旬至6月初。
-  - 第二阶段：7月至8月高温来临之前。
-- **推荐药剂**：
-  - 成虫控制：15%哒螨灵乳油稀释1,500倍。
-  - 卵控制：24%螺螨酯悬浮剂稀释3,000倍。
-  - 虫病兼防：1.8%阿维菌素稀释1,500～2,000倍加上80%代森锰锌稀释500～800倍。
-- **喷药顺序**：先处理树冠内部及下部区域，然后转向外部及上部；特别注意喷洒叶背面及果实阴暗面。
-- **冬季清园**：使用浓度为0.8°Bé的石硫合剂消灭越冬螨虫。
-请注意，如果您的问题中的“红蜘蛛”指的是其他特定种类，请提供更多详细信息以便给出更准确的答案。此外，对于任何化学农药的应用，请严格按照产品说明书操作，并考虑环境安全因素。</t>
+          <t>针对红蜘蛛（橘全爪螨）对脐橙的危害，可以采取以下措施进行防治：
+1. **监测预警**：定期检查叶片背面及枝叶间缝隙，当平均每片叶子上的红蜘蛛数量达到或超过2头时，即应开始用药。
+2. **化学防治**：
+   - 第一次施药建议使用乙唑螨腈与阿维菌素混合液，这两种药物组合能有效杀死成螨和若螨。
+   - 七天后再次施药，可选用苯肼酯等药物，这类药物主要针对若螨和卵。
+   - 喷洒时要特别注意喷透叶背以及枝条间的缝隙，确保全面覆盖。
+3. **轮换用药**：鉴于赣南地区已发现多个红蜘蛛种群对阿维菌素、哒螨灵、乙螨唑、螺螨酯产生了抗药性，因此在实际操作中应当建立合理的轮换用药机制，避免长期单一使用某一种杀螨剂导致害虫产生抗药性。
+4. **生物防治**：推广使用尼氏钝绥螨、胡瓜钝绥螨等天敌来控制红蜘蛛的数量。同时，在果园内适当种植草本植物也有利于保护这些有益昆虫。
+5. **农业管理**：通过合理修剪改善果园内的小气候条件，比如增强通风透光性能；及时清理园地减少病虫源基数；保持良好的土壤湿度以抑制红蜘蛛的繁殖。
+综上所述，对于红蜘蛛的防控需要综合运用多种手段，并且要注意根据实际情况灵活调整策略。</t>
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -1795,24 +1857,66 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>知识库中没有找到关于脐橙介壳虫具体防治方法的信息。对于脐橙的病虫害防治，资料中提到了一些通用的原则和针对其他特定害虫（如柑橘全爪螨）或病害（如炭疽病）的方法，但未直接提及介壳虫的防治措施。
-如果需要了解介菌虫的具体防治方法，建议参考专业的农业技术指导书籍或者咨询当地的农业技术服务部门获取更准确的信息。同时，可以考虑遵循以下一般性建议来减少果园内害虫的发生：
-- 采用绿色防控思路，比如通过监测预警、合理修剪改善果园小气候等手段。
-- 清园工作也很重要，及时清除枯枝落叶，减少害虫越冬场所。
-- 保护天敌，利用自然界的生物控制机制来抑制害虫数量。
-- 实施精准施药策略，在必要时选择合适的农药，并按照推荐剂量使用，避免过度依赖化学农药导致抗药性的产生。</t>
+          <t>脐橙介壳虫的防治可以按照以下步骤进行：
+### 1. 冬季清园（物理/农业防治）
+- **目标**：降低越冬虫源基数，这是全年防治最省力的关键环节。
+- **措施**：
+  - 修剪受害严重的枯枝、过密枝，并集中销毁。
+  - 喷施99%矿物油100～150倍液+石硫合剂，以物理封杀越冬成虫。
+### 2. 生长期防治（核心防治期）
+- **关键**：抓住若虫孵化盛期（蜡壳尚未形成，此时药效最好）。
+- **防治时期**：
+  - 第一代若虫（最关键）：4月下旬至5月中旬
+  - 第二代若虫：7月中旬至8月中旬
+- **监测方法**：观察枝干及叶背，发现细小粉白色幼虫爬行时立即施药。
+### 3. 用药注意事项
+- **成虫阶段（有厚壳）**：必须添加矿物油或有机硅助剂，否则药剂无效。
+- **4～5月**：进行第一波压制，阻断全年爆发。
+- **采摘前用药**：注意安全间隔期，选用低残留药剂。
+- **密植果园**：优先结构化修剪，改善通风条件。
+### 4. 防治失败常见原因
+- **时机不对**：成虫期用药，药液被介壳挡住。
+- **喷施不透**：叶背、枝条分叉处有死角残留。
+- **未加助剂**：未使用矿物油类渗透剂，无法溶解蜡质保护层。
+### 5. 生态防治
+- **保护天敌**：红点唇瓢虫、草蛉、蚜小蜂。
+- **天敌活跃期**：严禁大面积使用高毒广谱性杀虫剂。
+通过以上综合措施，可以有效控制脐橙介壳虫的危害。</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>知识库中没有找到关于脐橙介壳虫具体防治方法的信息。根据提供的资料，主要讨论了柑橘全爪螨、脐黄落果的防治以及炭疽病等其他病虫害的管理措施，但未直接提及介壳虫及其防治策略。如果需要了解介壳虫的具体防治方法，建议参考专门针对该类害虫的农业指导材料或咨询相关专业人士。</t>
+          <t>脐橙介壳虫的防治可以分为三个主要阶段，具体措施如下：
+### 1. 冬季清园（物理/农业防治）
+- **目标**：降低越冬虫源基数，这是全年防治最省力的关键环节。
+- **具体措施**：
+  - 修剪受害严重的枯枝、过密枝，并集中销毁。
+  - 喷施99%矿物油100～150倍液+石硫合剂，以物理封杀越冬成虫。
+### 2. 生长期防治（核心防治期）
+- **关键**：抓住若虫孵化盛期（蜡壳尚未形成，此时药效最好）。
+- **防治时期**：
+  - 第一代若虫（最关键）：4月下旬至5月中旬
+  - 第二代若虫：7月中旬至8月中旬
+- **监测方法**：观察枝干及叶背，发现细小粉白色幼虫爬行时立即施药。
+- **注意事项**：
+  - 成虫阶段（有厚壳）必须添加矿物油或有机硅助剂，否则药剂无效。
+  - 密植果园优先进行结构化修剪，改善通风条件。
+  - 采摘前用药需注意安全间隔期，选用低残留药剂。
+### 3. 生态防治
+- **保护天敌**：红点唇瓢虫、草蛉、蚜小蜂等。
+- **注意事项**：在天敌活跃期严禁大面积使用高毒广谱性杀虫剂。
+### 防治失败常见原因
+- 时机不对：成虫期用药，药液被介壳挡住。
+- 喷施不透：叶背、枝条分叉处有死角残留。
+- 未加助剂：未使用矿物油类渗透剂，无法溶解蜡质保护层。
+通过上述综合措施，可以有效控制脐橙介壳虫的危害。</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -1838,41 +1942,37 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>潜叶蛾的防治可以从以下几个方面进行：
+          <t>潜叶蛾的防治措施主要包括农业防治、物理防治和化学防治三个方面，具体如下：
+1. **农业防治**：
+   - 抹除零星夏梢，统一放梢以缩短潜叶蛾的危害期。
+   - 冬季进行清园工作，剪除受虫害影响的枝条。
+2. **物理防治**：
+   - 每2公顷设置1盏太阳能杀虫灯。
+   - 在新梢生长期挂设黄板，密度为20张/667平方米。
+3. **化学防治**：
+   - 当新梢长至1～2厘米时，可选用以下药剂之一进行喷施：
+     - 2.5%功夫乳油稀释2000倍液
+     - 20%除虫脲悬浮剂稀释1500倍液
+以上方法结合使用可以有效控制潜叶蛾对脐橙树的危害。请注意按照推荐剂量使用农药，并遵循安全操作规程。</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>潜叶蛾的防治措施主要包括农业防治、物理防治和化学防治三个方面，具体如下：
 1. **农业防治**：
    - 抹除零星夏梢，统一放梢以缩短危害期。
-   - 冬季清园时剪除虫枝。
+   - 冬季进行清园工作，剪除带有虫害的枝条。
 2. **物理防治**：
    - 每2公顷设置1盏太阳能杀虫灯。
-   - 在新梢期挂黄板，每667平方米挂20张。
+   - 在新梢生长期间挂设黄板，密度为20张/667平方米。
 3. **化学防治**：
-   - 当新梢长到1～2厘米时，可以喷洒2.5%功夫乳油稀释2000倍液或20%除虫脲悬浮剂稀释1500倍液。
-以上措施结合使用，能够有效控制潜叶蛾的危害。需要注意的是，在施药过程中应严格按照推荐浓度稀释药剂，并且交替使用不同作用机理的药剂，避免害虫产生抗药性。同时，选择无风晴天早晚施药，避开高温（&gt;30℃）、降雨、大风天气，确保叶片正反面及内膛均匀着药，但不要让叶面积水滴落。此外，在果实采收前15至30天停止使用化学药剂。</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>根据提供的参考资料，潜叶蛾的防治措施可以分为农业防治、物理防治和化学防治三类。具体如下：
-### 1. 农业防治
-- 抹除零星夏梢，统一放梢以缩短潜叶蛾的危害期。
-- 冬季进行清园工作，剪除带有虫害的枝条。
-### 2. 物理防治
-- 每2公顷设置1盏太阳能杀虫灯。
-- 在新梢生长期间挂设黄板，密度为每667平方米挂设20张。
-### 3. 化学防治
-- 当新梢长度达到1～2厘米时，可选用以下药剂之一进行喷施：
-  - 2.5%功夫乳油稀释至2000倍液。
-  - 20%除虫脲悬浮剂稀释至1500倍液。
-请注意，在实施化学防治时应遵循精准施药的原则，包括但不限于：
-- 严格按照推荐浓度稀释药剂，避免随意混配。
-- 交替使用不同作用机理的药剂，以延缓抗药性的产生。
-- 选择无风且天气晴朗的日子早晚施药，避开高温（&gt;30℃）、降雨或大风天气。
-- 使用雾化效果良好的电动喷雾器，确保叶片正反面及树冠内部都能均匀着药，但不要让叶面积水滴落。
-- 在果实采收前15～30天停止使用任何化学药剂。
-以上就是关于潜叶蛾防治的主要措施。希望这些信息对您有所帮助！</t>
+   - 当新梢长到1～2厘米时，可以喷施以下药剂之一：
+     - 2.5%功夫乳油稀释至2000倍液。
+     - 20%除虫脲悬浮剂稀释至1500倍液。
+以上方法结合使用，能够有效控制潜叶蛾的危害。同时，请注意按照施药通用规范操作，比如选择无风晴天早晚施药，避免高温（&gt;30℃）、降雨或大风天气，并确保叶片正反面及内膛均匀着药等。</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
@@ -1902,11 +2002,10 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>知识库中没有直接提到脐橙一年需要施几次肥以及具体的施肥时间。但是，根据提供的资料可以了解到一些关于施肥的原则和建议：
-- 施用农家肥和生物有机肥能够提高果实品质，而长期单一使用化肥会导致品质下降。
-- 有机液肥与化肥配合使用对幼树生长有利，特别是植物源有机液肥与化肥各占50%的处理效果较好。
-- 在施肥时还需要考虑到土壤中的微生物生态，比如高氮环境会抑制有益菌根真菌（AM真菌）的发展。
-为了获得更准确的施肥次数及时间安排，建议参考专业的脐橙种植指南或咨询农业专家。通常情况下，果树的施肥计划会依据其生长周期、土壤状况以及当地气候条件来制定。</t>
+          <t>根据提供的参考资料，关于脐橙施肥的具体次数和时间点没有直接给出一个统一的答案。但是，资料中提到了一些具体的施肥建议，可以作为参考：
+1. **幼树（2～4年生）**：推荐每年施用均衡复合肥（N:P:K=15:15:15）400 g/株，并且在冬季施加有机肥2.5 kg/株。这里提到的是年度总量而非具体分几次施用。
+2. **结果树（9年以上）**：对于已经进入结果期的树木，建议使用高氮复合肥（22:4:4）1 000 g/株 + 高钾复合肥（20:5:20）2 500 g/株 + 均衡复合肥1 000 g/株，并且同样是在冬季施加有机肥5 kg/株。同样地，这给出了总的肥料用量但未明确指出一年内应分为几次施用。
+综上所述，虽然资料提供了不同生长阶段脐橙树所需肥料的大致种类与数量，但对于“一年需要施几次肥”以及“具体什么时候施”的问题，资料中并没有给出详细的指导。因此，基于现有信息无法提供确切答案。实际操作时可能还需要结合当地气候条件、土壤状况等因素灵活调整施肥计划。如果需要更精确的信息，建议咨询专业的农业技术人员或查阅更多相关文献。</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
@@ -1914,15 +2013,15 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>知识库中没有直接提到脐橙一年需要施几次肥以及具体的施肥时间。不过，根据提供的资料，可以了解到一些关于施肥的原则和建议：
-1. **施肥原则**：推荐使用有机肥（如农家肥、生物有机肥）与化肥相结合的方式进行施肥，以提高果实品质并维持土壤健康。长期单一施用化肥会导致酸含量升高、品质下降。
-2. **幼树施肥**：对于纽荷尔脐橙幼树而言，动植物源有机液肥单独施用或与化肥配合施用均能促进其生长。特别是当植物源有机液肥与化肥各占50%时，效果更佳。
-3. **根际微生物生态**：施肥管理还需要考虑到对根际微生物生态的影响，比如AM真菌的活动，高氮环境会抑制这些有益微生物的作用。
-虽然上述信息提供了关于如何施肥的一些建议，但具体到每年施肥次数及最佳施肥时机，则需要参考更多专门针对脐橙施肥周期的研究或指南。如果您的问题更加具体化，例如针对某个特定品种或者特定条件下的脐橙种植，请提供更多信息以便给出更准确的答案。</t>
+          <t>根据提供的参考资料，成年结果树的脐橙每年需要施肥3～4次。具体的施肥时间没有详细列出，但可以参考以下原则进行：
+- **重施基肥**：通常在秋季果实采收后至春季萌芽前施用，以有机肥为主。
+- **看树补肥**：根据树体的具体生长情况适时补充肥料。
+- **关键期追肥**：在脐橙生长的关键时期（如花芽分化期、果实膨大期等）进行追肥。
+资料中提到的是施肥的总体频次和原则，并未具体到每个月份或每个生长阶段的确切时间点。因此，建议结合当地气候条件及脐橙的实际生长状况来确定具体的施肥时机。</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1948,31 +2047,70 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>知识库中没有找到关于脐橙缺钙具体表现的直接描述。但是，根据提供的资料，可以了解到一些与脐橙营养管理相关的信息：
-- 一些产区存在钙等中微量元素不足的问题（资料1）。
-- 含钙镁及硼、锌等微量元素的复合镁肥，以及土施和叶面补施结合，较有利于纠正隐性缺素（资料4）。
-对于如何补充钙元素，虽然资料中没有直接提到针对钙的具体补充方法，但基于上述信息，我们可以推测出几种可能的方法来改善钙缺乏的情况：
-1. 使用含钙的复合肥料：选择含有钙以及其他微量元素如镁、硼、锌的复合肥料进行土壤施肥。
-2. 土壤施用与叶面喷施相结合：除了通过根部吸收外，还可以考虑采用叶面喷施的方式直接向植物提供钙元素。
-请注意，这些建议是基于现有资料做出的一般性建议，并非专门针对脐橙缺钙情况的具体指导。为了更准确地解决脐橙缺钙问题，建议咨询专业的农业技术人员或参考更多专业文献。</t>
+          <t>脐橙缺钙的表现及补充方法如下：
+### 缺钙表现
+根据资料，脐橙缺钙主要表现在以下几个方面：
+1. **新梢嫩叶**：叶尖黄化，叶缘向内卷曲，叶片小而厚，严重时呈"钩状"畸形。
+2. **新梢顶端**：从顶端向下枯死，出现秃枝现象。
+3. **果实**：裂果增多、浮皮果、软果，耐储性下降，日灼加重。
+4. **根系**：根尖变黑腐烂，侧根丛生呈"狮子尾根"。
+### 补钙方案
+#### 1. 土壤改良（治本）
+- **酸碱度调节**：
+  - 使用材料：熟石灰 / 硅钙镁肥
+  - 施用时期：冬季清园期
+- **底肥增钙**：
+  - 使用材料：钙镁磷肥 / 过磷酸钙
+  - 施用时期：结合冬肥深施
+#### 2. 叶面喷施（应急）
+- **谢花后 1～2 个月**：
+  - 推荐药剂：糖醇钙 / 螯合钙
+  - 目的：增强幼果果皮韧性
+- **果实膨大期（7～9月）**：
+  - 推荐药剂：硝酸铵钙 / 糖醇钙
+  - 目的：预防生理裂果
+&gt; 注意事项：避免高温施药，每隔 10～15 天一次，连续 2～3 次。
+### 常见误区
+1. **只喷叶不改土**：土壤酸化问题不解决，补钙效果会减半。
+2. **只在生长期补钙**：钙移动慢，冬季基肥施钙是基础。
+3. **选错钙肥**：糖醇螯合钙利用率远高于普通无机钙。
+通过上述措施，可以有效防治脐橙的缺钙症状。</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>知识库中没有找到关于脐橙缺钙具体表现的直接描述。但是，根据提供的资料，可以了解到一些与钙相关的管理信息：
-1. **钙的重要性**：钙是脐橙生长过程中所需的一种重要中量元素，对于维持细胞壁结构、促进果实发育等方面具有重要作用。
-2. **补充方法**：
-   - 资料提到含钙镁及硼、锌等微量元素的复合镁肥，以及土施和叶面补施结合的方式较有利于纠正隐性缺素问题（资料1）。虽然这里主要讨论的是镁，但同样适用于钙的补充。
-   - 通过使用石灰、牡蛎壳粉或含镁石灰等材料来调理酸化土壤，这不仅可以减缓土壤酸化过程，还能降低钙镁淋失的风险（资料8）。
-   - 增加有机肥和土壤调理剂的投入，并根据拮抗吸收关系同步补充钙、镁等元素，以实现平衡供肥（资料8）。
-综上所述，虽然没有直接说明脐橙缺钙的具体症状，但从施肥管理和土壤调理的角度给出了如何有效补充钙的方法。如果需要更详细的缺钙症状描述或其他特定建议，请参考更多专业文献或咨询农业专家。</t>
+          <t>### 脐橙缺钙的表现
+根据资料，脐橙缺钙主要表现在以下几个方面：
+- **新梢嫩叶**：叶尖黄化，叶缘向内卷曲，叶片小而厚，严重时呈"钩状"畸形。
+- **新梢顶端**：从顶端向下枯死，出现秃枝现象。
+- **果实**：裂果增多、浮皮果、软果，耐储性下降，日灼加重。
+- **根系**：根尖变黑腐烂，侧根丛生呈"狮子尾根"。
+### 缺钙的原因
+- 土壤酸化：如赣南红壤pH普遍低于5.0，导致钙离子被淋失。
+- 拮抗作用：过量施用铵态氮肥或钾肥，抑制了根系对钙的吸收。
+- 水分冲突：极端干旱或高湿条件下，蒸腾作用减弱，引发生理性缺钙。
+### 补钙方案
+#### 缺钙土壤改良（治本）
+- **酸碱度调节**：使用熟石灰或硅钙镁肥，在冬季清园期进行施用。
+- **底肥增钙**：结合冬肥深施钙镁磷肥或过磷酸钙。
+#### 缺钙叶面喷施（应急）
+- **谢花后1～2个月**：推荐使用糖醇钙或螯合钙，以增强幼果果皮韧性。
+- **果实膨大期（7～9月）**：建议喷施硝酸铵钙或糖醇钙，预防生理裂果。
+&gt; 注意事项：
+&gt;
+&gt; - 避免在高温条件下施药。
+&gt; - 每隔10～15天喷一次，连续2～3次为宜。
+### 常见误区
+1. 只喷叶不改土：如果土壤酸化问题没有得到解决，补钙效果会大大降低。
+2. 只在生长期补钙：由于钙移动缓慢，因此冬季基肥中施加钙是基础。
+3. 选择错误的钙肥类型：糖醇螯合钙的利用率远高于普通无机钙。</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -1998,21 +2136,23 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>脐橙叶片发黄可能是因为缺乏某些中微量元素，根据提供的资料，以下是一些可能导致叶片发黄的营养元素缺乏情况：
-- **钼**：钼缺乏可导致幼树叶片黄化和光合能力下降。如果怀疑是钼缺乏引起的问题，可以通过喷施钼酸铵来纠正。
-需要注意的是，虽然资料提到了镁肥对提高叶片营养水平有积极作用，以及硼、锌等微量元素的重要性，但直接指出这些元素缺乏会导致叶片发黄的信息并未在给定资料中明确提及。因此，对于叶片发黄的情况，建议首先考虑是否为钼缺乏所致，并结合土壤有效钼含量及叶片营养测定进行综合诊断。
-知识库中没有找到关于其他特定肥料（如氮、磷、钾或铁）缺乏直接导致脐橙叶片发黄的具体信息。因此，在实际操作中，还需要结合具体的田间观察和其他检测手段来确定确切原因。</t>
+          <t>根据提供的参考资料，脐橙叶片发黄可能与以下几种营养元素的缺乏有关：
+1. **钼**：资料中提到钼缺乏可导致幼树叶片黄化和光合能力下降。如果发现脐橙叶片出现黄化现象，尤其是幼树，可能是钼元素不足所致。可以通过喷施钼酸铵来纠正这种状况。
+2. **镁**：虽然直接关于镁缺乏引起叶片发黄的信息较少，但资料指出补镁可以提高叶片营养水平、单果质量和品质指标，特别是在土壤交换性镁偏低的情况下。因此，当脐橙园存在镁素不足时，也可能表现为叶片颜色异常，包括发黄。推荐采用土施加叶面喷施的方式补充镁肥。
+需要注意的是，除了上述两种元素外，还有其他因素如铁、锰等微量元素缺乏或过量，以及病虫害影响等都可能导致脐橙叶片变黄。具体原因需要结合实际情况（如土壤测试结果、植株生长状态等）进一步分析确定。此外，资料还特别强调了赣南多数脐橙园缺镁的情况，提示在该地区种植者应更加重视镁肥的应用。
+综上所述，针对脐橙叶片发黄的问题，首先考虑是否为钼或镁元素缺乏，并采取相应措施进行调整。同时建议进行全面的土壤及植物营养诊断以准确识别问题所在。</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>根据提供的参考资料，脐橙叶片发黄可能与以下几种中微量元素的缺乏有关：
-1. **钼**：资料指出，钼缺乏可导致幼树叶片黄化和光合能力下降。如果发现脐橙叶片出现黄化现象，可以考虑是否为钼元素不足所致。诊断时应结合症状、土壤有效钼含量以及叶片营养测定来确认，并可通过喷施钼酸铵作为纠正措施。
-2. **镁**：虽然直接提到镁缺乏会导致叶片黄化的信息不多，但资料强调了镁肥对于提高叶片营养水平的重要性，特别是在土壤交换性镁偏低的情况下。因此，当遇到叶片黄化问题时，也应检查土壤中的镁含量是否充足。
-需要注意的是，除了上述两种元素外，还有其他因素也可能引起脐橙叶片发黄，比如铁、锌等微量元素的缺乏或过量，以及病虫害的影响等。因此，在确定具体原因前，建议进行全面的土壤测试及植物营养分析。此外，资料中没有明确提及铁、锌等其他常见导致叶片黄化的元素缺乏情况，故无法进一步提供相关信息。</t>
+          <t>根据提供的资料，脐橙叶片发黄可能与以下几种中微量元素的缺乏有关：
+1. **钼**：资料中提到钼缺乏可导致幼树叶片黄化和光合能力下降。如果怀疑是钼缺乏引起的叶片黄化，可以通过喷施钼酸铵来纠正。
+2. **镁**：虽然直接提到镁缺乏会导致叶片黄化的信息不多，但资料强调了镁肥对提高叶片营养水平的重要性，特别是在土壤交换性镁偏低的情况下。因此，镁不足也可能间接引起叶片颜色变化。
+3. **其他因素**：除了上述两种元素外，资料还提到了钙、硼等中微量元素对于脐橙生长的重要性，但没有直接指出它们缺乏会导致叶片发黄。此外，生理性脐黄（一种果实脐部发黄的现象）被归因于树体营养分配或内分泌失调，并非由特定肥料缺乏引起。
+综上所述，当发现脐橙叶片发黄时，首先应考虑是否为钼缺乏所致，其次检查镁的状态。同时，建议结合具体的土壤测试结果及植株营养状况进行综合判断。如果问题持续存在或者情况复杂，最好咨询专业的农业技术人员以获得更准确的诊断和解决方案。</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
@@ -2042,17 +2182,20 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>知识库中没有找到关于脐橙修剪最合适时间的具体信息。提供的资料主要集中在果实采收标准、方法以及气候环境对脐橙种植的影响等方面，并未提及修剪的相关内容。因此，根据现有参考资料无法直接回答您的问题。对于脐橙的修剪管理，建议参考专业的果树栽培书籍或咨询农业技术专家获取更准确的信息。</t>
+          <t>根据提供的资料，关于脐橙修剪的具体时间没有直接提到。但是，资料中提到了一些与修剪相关的操作时间点，可以作为参考：
+1. **促花措施**：对于树势旺盛的初结果树，在9～10月期间可以通过适当修剪或环割来促进开花。
+2. **保花保果措施**：在花量较少的年份里，建议在开花前抹除春梢营养枝；而在花量较多的年份，则保留部分春梢并留5片叶摘心。
+综上所述，虽然没有明确指出脐橙的最佳修剪时间，但从上述信息可以看出，秋季（特别是9～10月份）是进行修剪以促进开花的一个合适时机。此外，根据实际情况调整春季的管理策略也很重要。不过，请注意这些信息可能并不全面覆盖所有类型的修剪需求，具体最佳修剪时间还需结合当地气候条件及果园具体情况确定。如果需要更详细的指导，建议咨询专业的农业技术人员。</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
           <t>脐橙的修剪时间根据树龄和生长阶段有所不同，具体如下：
 - **幼树期（1～3年）**：
-  - 以摘心、抹芽、拉枝为主，轻剪促冠。
+  - 以轻剪为主，主要进行摘心、抹芽、拉枝等操作。
   - 春/秋梢长至15～20 cm时，留6～8片叶摘心；夏梢旺盛时约20 cm摘心。
   - 顶端丛生枝按"三疏一、五疏二"原则疏剪；有花蕾全部抹除。
   - 每年早春疏剪过密的、纤弱的、有枝无叶的枝条。
@@ -2067,7 +2210,7 @@
   - 小年（花量少）：保花保果为主，短截回缩结果枝组，轻剪保叶。
   - 第二次生理落果结束后（6月中旬～7月上旬）进行夏季修剪，主要疏除直立枝和下部裙枝。
   - 夏秋梢处理原则：短强留中去弱。
-综上所述，脐橙的修剪应根据不同生长阶段选择合适的时间点进行。幼树期主要在春、夏、秋季进行轻剪；初结果期则集中在春季萌芽前及夏季；盛果期则需要在春季萌芽前、第二次生理落果后以及夏季进行修剪。</t>
+总体来说，脐橙的修剪应遵循“因树制宜、轻重结合”的原则，保持“上稀下密、外疏内透”，实现立体结果。对于结果树，修剪时应遵循“剪上不剪下、剪外不剪内、剪强不剪弱”的原则。</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
@@ -2098,15 +2241,15 @@
       <c r="E14" s="4" t="inlineStr">
         <is>
           <t>脐橙的保花保果措施主要包括以下几个方面：
-- **初花期喷施营养液**：在脐橙树开花初期，可以通过喷施硼砂、磷酸二氢钾以及硝酸钾来促进花朵健康发育。
-- **谢花3/4后的处理**：
-  - 使用赤霉素30～50 mg/L加上0.075%芸苔素稀释至3,000～4,000倍液进行喷雾。
-  - 或者采用1克赤霉素（先用75%酒精溶解）与30克细胞分裂素混合后兑入30公斤水中制成溶液喷洒。此步骤建议重复两次，间隔时间为10～15天。
-- **针对壮旺树的操作**：对于生长旺盛但结果较少的树木，在第二次生理落果期间可以考虑对主干或主要枝条实施环割一周以促进果实留存。（注意：这种方法不适合于中等偏弱的树木）
-- **春梢管理**：
-  - 在那些已经连续多年开花结果的植株上，保留部分春季新生长出来的营养枝，并且当这些新枝长出大约五片叶子时进行摘心处理。
-  - 如果预计当年花量较少，则应在开花前及时去除过多的春梢。
-以上就是根据现有资料整理出的关于脐橙保花保果的主要方法。请注意，实际操作时还需结合当地气候条件及果园具体情况灵活调整。</t>
+1. **初花期喷施营养物质**：
+   - 在初花期，可以喷施硼砂、磷酸二氢钾以及硝酸钾等营养物质来促进花朵健康发育。
+2. **谢花3/4后的处理**：
+   - 当花朵凋谢达到约75%时，推荐使用赤霉素（浓度为30～50 mg/L）加上0.075%芸苔素稀释至3,000～4,000倍液进行喷雾。
+   - 或者采用另一种配方：将1克赤霉素（需先用75%酒精溶解）与30克细胞分裂素混合后兑入30千克水中制成溶液进行喷洒。此操作建议在首次喷施后10到15天重复一次以增强效果。
+3. **针对不同树势采取相应措施**：
+   - 对于生长旺盛但尚未大量结果的树木，在第二次生理落果期间可以通过环割主干或主要枝条一周的方式来促进果实保留。（注意：中等及以下长势的树木不宜采用此法）
+   - 如果预计当年开花量较少，则应在开花前去除春梢上的营养枝；相反地，如果预测开花数量较多，则应保留部分春梢，并在其上留下大约五片叶子后进行摘心处理。
+以上就是根据现有资料整理出的关于脐橙保花保果的主要方法。请注意实际应用时还需结合当地具体条件灵活调整。</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
@@ -2114,16 +2257,17 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>根据提供的参考资料，脐橙保花保果的方法主要包括以下几个方面：
-1. **初花期喷施营养元素**：
-   - 在初花期时，可以喷施硼砂、磷酸二氢钾以及硝酸钾等肥料来促进花朵的健康发育。
+          <t>根据提供的资料，脐橙保花保果的方法主要包括以下几个方面：
+1. **初花期喷施营养物质**：
+   - 在初花期，可以喷施硼砂、磷酸二氢钾、硝酸钾等营养物质，以促进花的健康发育。
 2. **谢花3/4后的处理**：
-   - 当花朵凋谢达到约75%时，推荐使用赤霉素（浓度为30～50 mg/L）加上芸苔素（稀释比例为3,000～4,000倍），或者将1克赤霉素（用75%酒精溶解）与30克细胞分裂素混合后兑入30公斤水中制成溶液进行喷雾。此操作建议重复两次，间隔时间为10至15天。
-3. **壮旺树的特殊管理**：
-   - 对于生长旺盛但结果较少的树木，在第二次生理落果期间可以通过环割主干或主要枝条一周的方式来促进果实保留。需要注意的是，这种方法不适用于生长状况中等到较差的树木。
-4. **春梢管理**：
-   - 在开花较多的年份里，应该保留部分春季新长出的枝条作为营养枝，并且在这些枝条上留下大约5片叶子之后进行摘心处理；而在花量较少的情况下，则应在开花前去除所有新生的春梢。
-通过上述措施，可以有效地提高脐橙的坐果率并保证果实的质量。不过，请注意实际操作时还需结合当地的具体条件及果园实际情况灵活调整。</t>
+   - 当花朵谢落达到3/4时，使用赤霉素（浓度为30～50 mg/L）加上0.075%芸苔素（稀释比例为3,000～4,000倍），或者将1克赤霉素（用75%酒精溶解）与30克细胞分裂素混合后兑入30公斤水中进行喷雾。建议在首次喷施后的10到15天内再重复一次该操作。
+3. **针对不同树势采取措施**：
+   - 对于生长旺盛但刚开始结果的树木，在9月至10月期间可以通过适当修剪或环割来促进开花。
+   - 如果是多年开花且花量较大的年份，则应保留部分春季新梢并留5片叶子进行摘心；而在花量较少的年份，则应在开花前去除春梢上的营养枝条。
+4. **第二次生理落果期管理**：
+   - 对于强壮且旺盛生长的树木，在第二次生理落果期间可以在主干或主要枝条上做一圈环割处理（注意：中等至弱小的树木不适合此方法）。
+通过上述措施，可以帮助提高脐橙的坐果率和果实质量。需要注意的是，具体操作时还需结合当地实际情况及专业指导来进行调整。</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
@@ -2153,29 +2297,29 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>根据提供的参考资料，脐橙的种植密度建议如下：
-- 科学合理的种植密度为625~1250株/公顷（hm²）。
-- 常用的具体株行距配置有两种推荐方案：
-  - 3米×4米
-  - 4米×4米
-此外，对于不同地形条件下的具体布局还有以下建议：
-- 对于平地和坡度小于等于15°的缓坡地，适合采用“宽行窄株”的栽培方式，推荐的行距为5.5至6.0米、株距为2至3米。
-- 在坡度介于16°到25°之间的丘陵山地区域，则更适宜采取“陡坡窄梯、密植小树冠”的模式，此时梯田带面宽度应尽量达到或超过3米，而株距则建议保持在2.0至2.5米之间。
-综上所述，选择合适的种植密度时需要综合考虑土地的具体情况如地形坡度等因素来决定最佳方案。</t>
+          <t>根据提供的参考资料，脐橙的种植密度可以根据不同的地形条件和管理模式进行调整：
+1. **宜机化建园条件下**：
+   - 对于坡度15°以下的地块，推荐采用“宽行窄株”模式，行距约为5.5～6.0米，株距为2～3米。
+   - 在16°～25°的丘陵山地，则建议采取窄梯、密植、小树冠的方式布局，并且需要预留出机耕道的空间。
+2. **常规人工或精细化管理下**：
+   - 根据具体的地形特点以及预期形成的树形大小，株行距可以控制在大约3米左右。按照这样的间距安排，每公顷（hm²）可种植约750～900株脐橙树。
+   - 另外还提到了一种4米×3米配置的成龄果园设置，这种布局主要用于滴灌试验。
+综上所述，脐橙的具体种植密度需结合实际地理环境及栽培目的来确定，但一般而言，在考虑机械化操作的前提下，合理的种植密度范围大致为每公顷750至900株之间。对于特定情况下的详细规划，请参考上述指导原则并结合实际情况灵活调整。</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>根据提供的参考资料，脐橙的种植密度建议如下：
-1. **科学种植密度**：一般推荐的科学种植密度为625~1250株/公顷（资料3）。
-2. **常用株行距**：
-   - 常见的配置包括3米×4米或4米×4米（资料3）。
-   - 在宜机化建园条件下，对于坡度15°以下的土地，推荐采用“宽行窄株”模式，行距约为5.5～6.0米、株距2～3米；而对于16°～25°的丘陵山地，则建议采用窄梯、密植、小树冠模式，并预留机耕道（资料4和资料6）。
-   - 对于常规人工或精细化管理模式下的果园，株行距可以根据地形和目标树形控制在约3米左右，折算后的种植密度大约为750～900株/公顷；也有报道提到使用4米×3米的成龄园配置用于滴灌试验（资料6）。
-综上所述，具体的种植密度需要根据实际的地理条件（如坡度）、管理方式（是否机械化操作）以及预期的树形等因素综合考虑来确定。</t>
+          <t>根据提供的参考资料，脐橙的种植密度可以根据不同的地形条件和管理模式进行调整：
+1. **宜机化建园条件下**：
+   - 坡度15°以下的平地或缓坡地适合采用“宽行窄株”模式，推荐的行距约为5.5～6.0米，株距为2～3米。
+   - 16°～25°的丘陵山地则建议采用窄梯、密植、小树冠模式，并预留机耕道。
+2. **常规人工或精细化管理模式下**：
+   - 株行距可根据具体地形和目标树形控制在约3米左右，折算后的种植密度大约为750～900株/公顷（hm²）。
+   - 另外也有提到4米×3米的成龄园配置用于滴灌试验的情况。
+综上所述，脐橙的具体种植密度需要根据实际的地理环境（如坡度）、土壤条件以及是否采用机械化管理等因素综合考虑来确定。资料中提供了几种典型的配置方案供参考，但最终选择还需结合实际情况灵活调整。</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
@@ -2205,12 +2349,12 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>根据提供的参考资料，脐橙果实套袋的好处主要包括：
-1. **保护果实**：通过使用抗风抗雨、透气性好的单层透光纸袋（或柑橘专用单层纸袋），可以有效减少外界环境对果实的直接伤害，比如风雨侵蚀、病虫害侵袭等。
-2. **改善外观品质**：套袋有助于提高脐橙果皮的光滑度和色泽均匀性，从而提升其商品价值。这是因为袋子能够阻挡部分阳光直射，避免了因强烈日照造成的日灼现象，同时也减少了农药残留于果面上的机会。
-3. **促进成熟**：适当的遮光作用有利于调节果实内部温度与湿度条件，对于促进果实正常发育及成熟有一定帮助。
-4. **便于管理**：在进行套袋操作时通常会先对果园进行全面的杀菌杀虫处理，这不仅为后续果实生长提供了更加清洁健康的环境，也简化了后期病虫害防治工作。
-综上所述，合理地实施套袋技术是提高脐橙产量质量的有效措施之一。但需要注意的是，在选择套袋材料以及具体实施过程中还需结合当地实际情况灵活调整，以达到最佳效果。</t>
+          <t>根据提供的参考资料，脐橙果实套袋的好处主要包括以下几点：
+1. **保护果实免受病虫害侵害**：通过在套袋前全园喷施一次杀菌剂和杀虫剂，并且使用抗风抗雨、透气性好的单层透光纸袋（或柑橘专用单层纸袋），可以有效减少病虫对果实的直接危害。
+2. **改善外观质量**：套袋能够避免果实表面受到机械损伤以及日灼等自然因素的影响，有助于提高果实的商品外观品质。
+3. **减少农药残留**：由于套袋后减少了直接向果实喷洒农药的需求，因此可以在一定程度上降低果实表面的农药残留量，更符合绿色食品生产的要求。
+4. **促进均匀着色**：虽然资料中没有明确提到这一点，但通常情况下，适当的遮光处理可以帮助果实更好地进行色素积累，从而达到更加均匀美观的颜色分布。不过，请注意这需要基于特定类型的袋子材质来实现最佳效果。
+综上所述，给脐橙果实套袋是一种有效的管理措施，旨在提高果实的安全性和市场价值。</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
@@ -2219,12 +2363,13 @@
       <c r="G16" s="4" t="inlineStr">
         <is>
           <t>脐橙果实套袋的好处主要包括以下几点：
-1. **提高果实外观品质**：套袋可以减少果实表面的机械损伤和病虫害侵袭，使果皮更加光滑细腻，色泽均匀，从而提升果实的商品价值。
-2. **减少农药残留**：通过物理隔离的方式减少了直接喷洒在果实上的农药量，有助于降低果实中的农药残留，满足市场对绿色安全食品的需求。
-3. **防病虫害**：套袋能够有效阻挡部分病菌孢子及昆虫接触果实的机会，减少如炭疽病等病害的发生率，同时也能防止鸟类啄食。
-4. **调节微环境**：纸袋内部形成一个相对稳定的温湿度小环境，有利于果实正常发育，特别是在极端天气条件下（如高温、干旱或暴雨）为果实提供保护。
-5. **促进着色**：对于某些品种而言，适当遮光处理还能改善果实颜色，使其达到更理想的成熟状态下的色泽表现。
-综上所述，合理实施套袋技术不仅能够显著改善脐橙果实的质量与安全性，还有助于增加种植者的经济效益。不过需要注意的是，在选择套袋材料时应选用透气性好且具有一定防水性能的产品，并按照正确的方法进行操作以确保效果。</t>
+1. **提高果实品质**：套袋可以改善果实的外观，使果皮更加光滑细腻，色泽均匀，从而提升商品价值。
+2. **减少病虫害**：通过物理隔离的方式，套袋能够有效防止多种病虫害直接侵害果实，如炭疽病、溃疡病等，减少了化学农药的使用量，有利于生产绿色健康的水果。
+3. **防日灼**：夏季强烈的阳光直射可能会导致果实表面出现日灼现象，影响其外观质量。套袋后可避免这种情况发生。
+4. **防裂果**：在雨季或灌溉不当的情况下，未套袋的果实容易因水分吸收过快而产生裂纹。套袋有助于保持果实周围环境相对稳定，降低裂果率。
+5. **促进着色**：对于某些品种而言，适当的遮光处理（如使用半透明袋子）可以帮助果实更好地着色，达到理想的成熟状态。
+6. **延长货架期**：套袋后的脐橙通常具有更好的耐贮性，能够在一定程度上延长其保鲜时间，便于长途运输及销售。
+综上所述，合理地进行果实套袋是提高脐橙产量与品质的重要措施之一。不过需要注意的是，在选择套袋材料时应确保其具备良好的透气性和透光性，并且操作过程中要严格按照技术要求执行，以充分发挥套袋的作用。</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
@@ -2254,28 +2399,51 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>根据提供的参考资料，关于脐橙采摘后的储存方法并没有直接详细的说明。但是，我们可以从资料中提取一些间接相关的信息来帮助理解如何更好地储存脐橙：
-1. **控制机械损伤**：脐橙在采收、运输和贮藏过程中容易因为挤压而受损，特别是当挤压位移超过约10毫米时，损伤风险会显著增加。因此，在储存前及储存期间需要注意避免过度挤压，并且应该使用适当的缓冲包装材料以及合理的堆码方式以减少物理伤害。
-2. **及时处理**：采收后的脐橙应在24小时内送往进行包装处理，这表明快速地将果实从田间转移到更受控的环境中对于保持其品质非常重要。
-3. **适宜条件下的保存**：虽然具体温度湿度等条件未被提及，但通常来说，水果类产品的冷藏可以延长保质期并保持新鲜度。考虑到脐橙属于柑橘类水果，一般建议将其存放在阴凉干燥处或冰箱内冷藏室里（非冷冻），同时注意不要让它们接触到直射阳光。
-4. **分级与挑选**：在储存之前对脐橙进行分级也很重要，包括按照糖度、大小、颜色等因素来进行筛选，这样不仅可以提高商品价值，也有利于根据不同质量标准采取相应的存储措施。
-综上所述，虽然没有提供非常具体的储存指南，但从上述几点可以看出，为了保证脐橙的质量，在储存时需要特别注意防止物理性损害、尽快完成初步加工流程、并在适当条件下存放。如果需要更加专业的储存技术指导，可能还需要查阅更多专门针对脐橙长期保存的专业文献。</t>
+          <t>根据提供的参考资料，脐橙采摘后的储存方法主要包括以下几个方面：
+1. **采后处理流程**：
+   - 采收成熟果
+   - 常温发汗
+   - 防腐保鲜处理
+   - 晾干
+   - 单果包装
+   - 入库贮藏
+   - 运输与货架销售模拟
+2. **贮藏环境控制**：温度、湿度、氧气、二氧化碳和乙烯等因子共同影响脐橙在贮藏期间的品质变化。理想的贮藏条件能够减缓硬度下降、可滴定酸减少、维生素C流失以及风味物质的损失，从而保持较高的感官满意度。
+3. **适宜的贮藏方式**：对于特定品种如赣南纽荷尔脐橙，采用较优的贮藏技术可以有效维持果实中的酸含量较高水平，同时降低乙醇乙醛积累，提高感官评价，并将可接受的贮藏寿命延长至大约160天左右。
+4. **避免不适当条件**：不当的贮藏条件会导致失重率增加、腐烂率上升、果实软化及风味变差等问题。值得注意的是，在这些不利因素中，营养成分和风味品质往往比外观特征更快地恶化。
+5. **机械损伤预防**：由于脐橙横向抗压能力较弱，在采收、运输及贮藏过程中容易受到挤压而受损。当挤压位移超过约10毫米时，损伤风险显著增大。因此，在整个物流链中需要采取措施来减少物理性损害，比如使用适当的缓冲材料进行包装并优化堆放方式。
+综上所述，通过科学合理的采后处理程序结合良好的贮藏管理实践，可以有效地延长脐橙的保存期限并保持其优良品质。</t>
         </is>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>根据提供的参考资料，关于脐橙采摘后的储存方法并没有直接提及具体的储存步骤或条件。但是，从资料中可以提取一些间接相关的信息来帮助理解如何更好地处理采收后的脐橙以保证其质量：
-- **及时处理**：采收后的脐橙应在24小时内送往包装处理（[资料1]、[资料2]）。
-- **避免露天堆放**：采下的果实不得露天堆放过夜（[资料1]、[资料2]），这意味着需要尽快将脐橙转移到适当的存储环境中。
-- **机械损伤控制**：考虑到脐橙在采收、运输和贮藏过程中容易受到挤压而受损（[资料5]），因此，在储存时应该注意使用合适的缓冲材料，并且合理安排堆码方式，减少物理性损伤的风险。
-然而，对于更详细的储存条件如温度、湿度等具体要求，知识库中没有找到相关信息。为了确保脐橙的最佳保存状态，建议参考专业农业书籍或者咨询专业人士获取更多关于脐橙储存的具体指导。</t>
+          <t>根据提供的参考资料，脐橙采摘后的储存方法主要包括以下几个方面：
+1. **采后处理流程**：
+   - 采收成熟果实。
+   - 常温下发汗（放置3天左右）。
+   - 进行防腐保鲜处理。
+   - 自然晾干。
+   - 单果包装（如使用0.02 mm聚乙烯薄膜）。
+   - 入库贮藏。
+   - 运输与货架销售模拟。
+2. **贮藏环境**：
+   - 温度、湿度、氧气、二氧化碳和乙烯等因子共同影响脐橙的品质变化。随着贮藏期延长，硬度、可滴定酸、维生素C、风味物质和感官满意度会逐步下降。
+   - 对于赣南纽荷尔脐橙而言，较优的贮藏方式可以保持更高的酸含量、更低的乙醇乙醛积累、更好的感官满意度，并将可接受贮藏寿命延长至约160天。
+3. **不同贮藏方式及其效果**：
+   - **通风库（常温库）**：温度变化幅度较大（3.2～20.6℃），相对湿度波动也大（44.4%～99.8%）。长期常温贮藏可能导致异味物质积累，影响感官品质。
+   - **气调库（CA库）**：温度变化幅度较小（2.1～20.3℃），相对湿度波动范围为42.5%～100%。与通风库相比，温度和相对湿度的变化趋势基本一致。
+   - **冷库**：温度维持在2.1～4.2℃之间，相对湿度较为稳定（64.4%～99.0%）。冷库能有效抑制果实呼吸，延缓果实软化，维持较好的果实硬度。
+4. **注意事项**：
+   - 不适宜的贮藏条件会导致失重率增大、腐烂率上升、果实软化和风味劣变，其中营养与风味品质通常比外观品质退化更快。
+   - 脐橙粒化在采摘期和贮藏期都可能发生，严重时可丧失食用价值，因此采后分级、内部缺陷检测和合理贮藏同样属于种植链条的重要延伸环节。
+综上所述，为了保证脐橙的最佳品质，建议采用冷库进行贮藏，并注意控制温度和湿度，同时遵循上述采后处理流程。</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -2301,56 +2469,49 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>根据提供的参考资料，为了延长脐橙的保质期，在采后处理方面可以采取以下措施：
-1. **控制机械损伤**：
-   - 脐橙在采收、运输和贮藏过程中容易因为挤压而受损，特别是其横向抗压能力较弱。
-   - 当挤压位移超过大约10毫米时，损伤的风险会显著增加。因此，在采收后的搬运及储存过程中需要特别注意减少对果实的压力，并且优化包装材料以及堆放方式以提供更好的缓冲保护。
-2. **合理安排采收时间与条件**：
-   - 选择合适的天气进行采摘非常重要，避免在雾天、露水未干、大风或刚下过雨的情况下采摘。
-   - 对于计划长期保存或者远距离销售的脐橙，建议在其达到8.5至9.5成熟度时提前几天采收；而对于直接消费的新鲜水果，则应在完全成熟后再行收获。
-   - 特别地，赣南早脐橙作为例子给出：用于贮藏的果品应在开花后约200天开始采摘，而供鲜食使用的则需等到花后约215天才可采收。
-3. **采用正确的采收技术**：
-   - 使用“两剪法”（即每个果实经过两次修剪）来确保果蒂平整。
-   - 按照从外到内、从下往上的顺序依次采摘。
-   - 在整个过程中都要做到轻拿轻放，尽量减少对果实的物理伤害。
-   - 及时剔除掉病虫害感染、形状异常或有裂纹的不合格果实。
-4. **及时处理与适当存储**：
-   - 采摘下来的脐橙不应露天堆放过夜，最好能在24小时内送往包装车间进行后续加工。
-   - 根据资料提示，虽然没有具体提到冷藏等方法，但结合常识可知，适当的低温环境有助于延长保鲜期。此外，利用自动分选设备和冷链物流系统也可以进一步提高产品的商品价值。
-综上所述，通过上述措施可以在一定程度上帮助延长脐橙的保质期限。不过需要注意的是，关于更详细的温度控制或其他特殊保鲜技术方面的信息，在给定的参考资料中并未提及。</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
           <t>根据提供的参考资料，为了延长脐橙的保质期，可以采取以下措施：
 1. **采收成熟度控制**：
-   - 对于鲜销果，在正常成熟后进行采收。
-   - 对于需要贮藏或远距离运输的果实，则建议在8.5～9.5成熟时采收，这比鲜销果要早几天。
+   - 对于需要贮藏或远距离销售的脐橙，在果实达到8.5～9.5成熟时进行采收，这比直接鲜销的果实要稍微早一些。例如，赣南早脐橙作为贮藏果品应在花后200天采摘。
 2. **正确的采收方法**：
-   - 使用两剪法（一果两剪），确保果蒂平剪。
-   - 采收顺序应该是先外后内、先下后上。
-   - 在整个过程中保持轻采轻放轻运的原则。
-   - 及时剔除病虫果、畸形果以及裂果等不合格品。
-3. **避免不利天气条件下采收**：
-   - 避免在雾天或者露水未干的情况下采摘。
-   - 大风天气也不适合采收。
-   - 如果最近有降雨或灌溉活动，至少等待一周后再开始采收工作。
-   - 采下的果实不应露天堆放过夜，应在24小时内送往包装处理。
-4. **适当的贮藏条件**：
-   - 贮藏环境中的温度、湿度、氧气、二氧化碳和乙烯等因素都会影响到脐橙的质量。随着贮藏时间的增长，果实硬度、可滴定酸含量、维生素C水平及风味物质会逐渐下降。
-   - 采用较优的贮藏方式能够帮助维持较高的酸含量、减少乙醇乙醛积累，并提高感官满意度，从而将可接受的贮藏寿命延长至约160天左右。
-   - 不合适的贮藏条件会导致失重率增加、腐烂率上升、果实软化以及风味变差等问题出现，其中营养与风味品质往往比外观品质退化得更快。
-5. **优化包装与运输过程**：
-   - 由于脐橙横向抗压能力较弱，在采收、运输及储存期间容易因挤压而受损。当挤压位移超过大约10毫米时，损伤风险显著增加。
-   - 因此，在采运过程中需要注意控制受压变形情况，并通过改善缓冲包装材料和堆码方式来降低机械损伤的可能性。
-综上所述，通过合理安排采收时间、采用科学的采收技术、提供适宜的贮藏环境以及加强物流环节中的保护措施，可以有效延长脐橙的保质期限。</t>
+   - 采用“两剪法”（一果两剪），确保果蒂平剪。
+   - 按照从外到内、从下到上的顺序采摘。
+   - 在整个过程中保持轻柔操作，避免对果实造成机械损伤。
+   - 避免在雾天、露水未干、大风天气以及雨后或灌溉后一周内采收。
+   - 确保病虫害果、畸形果及裂果被及时剔除。
+3. **采后处理流程**：
+   - 完成采收后的脐橙应尽快进入后续处理环节，理想情况下应在24小时内送至包装处理处。
+   - 商业化处理通常包括：常温发汗、防腐保鲜处理、晾干、单果包装等步骤。
+   - 使用自动分选设备结合冷链设施可以帮助提高商品化水平，并且有利于按照糖度、大小、颜色等因素进行分级。
+4. **优化贮藏条件**：
+   - 控制好贮藏环境中的温度、湿度、氧气、二氧化碳和乙烯浓度等因素，以减缓品质下降速度。
+   - 选择合适的贮藏方式对于保持脐橙的新鲜度至关重要。研究表明，良好的贮藏技术可以使赣南纽荷尔脐橙的可接受贮藏寿命延长至约160天左右。
+   - 注意防止因不当贮藏导致的失重率增加、腐烂率上升等问题。
+5. **减少机械损伤**：
+   - 脐橙横向抗压能力较弱，因此在搬运及堆放时需特别小心，避免过度挤压。
+   - 当挤压位移超过大约10毫米时，损伤风险显著增大，故而应该通过改进缓冲包装材料与堆码方式来降低这种风险。
+综上所述，通过合理安排采收时间、采用科学的采收方法、遵循规范化的采后处理程序以及创造适宜的贮藏环境，可以有效延长脐橙的保质期。</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>根据提供的参考资料，脐橙采后处理以延长保质期的方法主要包括以下几个步骤：
+1. **采收成熟果**：确保果实达到适当的成熟度再进行采摘。对于鲜销果来说，应在正常成熟时采收；而对于需要贮藏或远距离运输的果实，则建议在8.5～9.5成熟时提前几天采收。
+2. **常温发汗**：刚采摘下来的脐橙应先放置于常温下“发汗”约3天左右，这有助于减少果皮上的水分，降低病害发生几率。
+3. **防腐保鲜处理**：对经过发汗处理后的脐橙实施商业化的防腐保鲜措施，可以有效抑制微生物生长，延缓果实腐烂过程。
+4. **自然晾干**：完成防腐处理之后，让脐橙自然晾干表面残留的药剂或其他物质，避免包装时造成污染。
+5. **单果包装**：使用0.02毫米厚的聚乙烯薄膜对每个脐橙单独进行包装，这样不仅可以保护果实免受机械损伤，还能调节内部微环境，有利于保持品质。
+6. **入库贮藏**：
+   - 选择合适的贮藏方式至关重要。根据资料，采用冷库（机械制冷）的方式能够更好地控制温度（维持在2.1～4.2℃之间），并保持相对稳定的湿度（64.4%～99.0%），从而有效抑制果实呼吸作用，减缓软化速度，保持较好的硬度。
+   - 相比之下，通风库和气调库虽然也能提供一定的保存条件，但由于其温度和湿度波动较大，可能不利于长期储存。
+7. **合理控制机械损伤**：在整个采收、运输及贮藏过程中注意轻拿轻放，避免过度挤压导致果实受损。当挤压位移超过大约10毫米时，损伤风险显著增加，因此需优化缓冲包装材料与堆码方式来减少此类损害。
+通过上述一系列科学合理的采后处理措施，可以在很大程度上延长脐橙的保质期限，并保证其良好的食用品质。</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2376,25 +2537,24 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>根据提供的资料，赣南地区适合种植的脐橙品种主要是纽荷尔。具体来说：
-- 赣南脐橙以纽荷尔为绝对主栽品种。
-- 这些果园多分布在红壤、海拔100–300 m、坡度30°以下的区域。
-因此，如果您在赣南地区考虑种植脐橙，纽荷尔是一个非常合适的选择。</t>
+          <t>根据提供的参考资料，赣南地区适合种植的脐橙品种主要包括：
+1. **纽荷尔脐橙**：这是赣南地区的绝对主栽品种，在调查中的占比达到了85%以上。纽荷尔脐橙以其良好的果实外观、丰富的果汁含量、适中的甜酸比例以及浓郁的香气而受到欢迎，通常在11月中下旬成熟。
+2. **其他中熟品种**：除了纽荷尔之外，资料还提到了一些其他的中熟脐橙品种如龙回红脐橙、福本等也适合在该区域种植。
+3. **早熟品种**：对于希望提前上市销售的果农来说，可以考虑种植一些早熟品种，比如赣南早脐橙、安远早（赣脐橙5号）、雷早一号等。
+4. **晚熟品种**：虽然资料中列出了几种晚熟脐橙品种如伦晚脐橙、夏金等，但需要注意的是，如果冬季最低温度低于-2℃的话，则不建议发展12月以后成熟的晚熟脐橙品种。
+综上所述，纽荷尔脐橙是赣南地区最推荐种植的脐橙品种，同时也可以根据市场需求和个人偏好选择其他类型的早熟或中熟脐橙进行栽培。</t>
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>根据提供的参考资料，赣南地区适合种植的脐橙品种主要包括：
-1. **纽荷尔脐橙**：这是赣南最主要的脐橙主栽品种，占比达85%以上。该品种具有以下特点：
-   - 鲜食品质好、适应性广。
-   - 果实外观整齐、风味佳、可溶性固形物较高。
-   - 汁多、甜酸适口、香气浓，可食率约73%-75%。
-   - 一般在11月中下旬成熟。
-2. **赣南早**：这是一种早熟型脐橙材料，具有提早成熟和差异化上市的优势。虽然资料中提到它还需要结合抗逆性和品质稳定性进行综合评价，但其作为抗逆与早熟育种研究的重要资源，在特定条件下可能也是一个不错的选择。
-综上所述，纽荷尔脐橙是目前赣南地区最适宜且广泛种植的脐橙品种，而赣南早则可以作为一种补充选择，特别是在追求早熟市场优势的情况下。不过，请注意实际种植时还需考虑具体的立地条件（如土壤类型、海拔高度等）以及管理措施。</t>
+          <t>根据提供的资料，赣南地区适合种植的脐橙品种主要包括：
+1. **纽荷尔脐橙**：这是赣南地区的绝对主栽品种，占比达85%以上。该品种具有良好的果实外观、甜酸适口、香气浓郁的特点，可食率约73%-75%，一般在11月中下旬成熟。纽荷尔脐橙适应性广，是多地生产与研究的核心材料。
+2. **赣南早脐橙**：这是一种早熟型脐橙，在干旱胁迫试验中表现出与纽荷尔不同的生理和分子响应，可以作为抗逆与早熟育种研究的重要资源。它具有提早成熟的优势，有助于实现差异化上市。
+此外，还有其他一些品种如红肉脐橙、华脐、伦晚等也在赣南地区有所栽培，但它们不是主要推广种植的对象。
+综上所述，对于赣南地区而言，纽荷尔脐橙是最为推荐的种植选择，而赣南早脐橙则因其早熟特性也值得考虑。不过，请注意具体选择时还需结合当地的气候条件、土壤类型等因素综合考量。</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
@@ -2424,47 +2584,63 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>知识库中没有找到关于朋娜脐橙的具体信息，因此无法直接对比纽荷尔脐橙与朋娜脐橙之间的区别。但是，根据提供的资料，我可以总结出纽荷尔脐橙的一些特点：
-- **种植广泛性**：纽荷尔脐橙是中国最主要的脐橙主栽品种之一，在全国脐橙总种植面积中的占比达到80%～85%，尤其在赣南地区占比超过85%。
-- **引入时间**：该品种于1978年被引入中国。
-- **植物特性**：
-  - 树势较强，树冠呈圆头形。
-  - 叶片为椭圆形且颜色深绿，有翼叶。
-  - 花粉败育，意味着其果实通常是无核的。
-- **果实特征**：
-  - 果实形状为椭圆形，颜色为橙红色。
-  - 果肉汁多化渣，香味浓郁。
-  - 可食率约为73%～75%。
-  - 成熟期一般在每年的11月中下旬。
-由于缺乏朋娜脐橙的相关数据，我们无法提供两者之间具体的比较分析。如果需要了解朋娜脐橙的信息或更详细的对比，请提供额外的参考资料。</t>
+          <t>纽荷尔脐橙和朋娜脐橙的区别主要体现在以下几个方面：
+1. **起源**：
+   - 纽荷尔脐橙：华盛顿脐橙的早熟芽变，1978年引入中国。
+   - 朋娜脐橙：同样来源于美国加利福尼亚州，是华盛顿脐橙芽变选育的结果，也是在1978年引入中国的。
+2. **树势与树形**：
+   - 纽荷尔脐橙：树势较强，树冠呈圆头形，叶片为椭圆形且叶色深绿，有翼叶。
+   - 朋娜脐橙：树势中等，树冠紧凑呈圆头形，分枝较多，适合密植。
+3. **果实特征**：
+   - 纽荷尔脐橙：果实形状为椭圆形，颜色为橙红色，无核，果肉汁多化渣，香味浓郁。
+   - 朋娜脐橙：果实可以是圆球形或椭圆形，端正；颜色从橙黄到橙红不等，果皮较光滑；脐部多为闭脐或微开脐；口感上肉质脆嫩化渣，风味浓甜，香气浓郁；单果重约200～250g；可溶性固形物含量在12%～14%之间。
+4. **成熟期**：
+   - 纽荷尔脐橙的具体成熟时间未在提供的资料中明确给出。
+   - 朋娜脐橙：属于早熟品种，在赣南地区大约于11月上中旬成熟，比纽荷尔略早。
+5. **栽培地位**：
+   - 根据资料，纽荷尔脐橙是中国脐橙中栽培面积最大的品种（占比85%以上）。
+   - 对于朋娜脐橙的栽培规模没有直接提及，但提到了其具有投产快（第3年）、抗寒性强、丰产性极强等特点。
+综上所述，虽然两者都是优秀的脐橙品种，但在具体特性如树形、果实外观及内部品质等方面存在差异。此外，纽荷尔脐橙在中国的种植更为广泛。</t>
         </is>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>知识库中没有找到关于朋娜脐橙的具体信息，因此无法直接对比纽荷尔脐橙和朋娜脐橙的区别。但是，根据提供的资料，我可以总结出纽荷尔脐橙的一些特点：
-1. **种植广泛性**：纽荷尔脐橙是中国最主要的脐橙主栽品种之一，在全国脐橙总种植面积中的占比达到80%～85%以上，在赣南产区的占比甚至超过85%。
-2. **引入时间与背景**：该品种是华盛顿脐橙的一个早熟芽变种，于1978年被引入中国。
-3. **植物学特性**：
-   - 树势较强。
-   - 树冠呈圆头形。
-   - 叶片为椭圆形且颜色深绿，有翼叶。
-   - 花粉败育，意味着其果实通常是无核的。
-4. **果实特征**：
-   - 果实形状为椭圆形。
-   - 颜色为橙红色。
-   - 果肉汁多、化渣（即果肉容易分离），香味浓郁。
-   - 无核。
-   - 可食率大约在73%到75%之间。
-   - 成熟期一般在每年的11月中下旬。
-5. **品质评价**：不同产地的纽荷尔脐橙在鲜汁品质上存在显著差异，特别是在有机酸、氨基酸、总酚、总黄酮以及风味物质组成等方面。其中，来自赣南地区的样品被认为具有较高的感官接受度及适宜的酸度水平。
-由于缺乏关于朋娜脐橙的信息，请您提供更多信息或具体方面的需求以便进一步帮助解答。</t>
+          <t>纽荷尔脐橙和朋娜脐橙在多个方面存在区别，根据提供的参考资料，可以总结如下：
+### 1. 起源
+- **纽荷尔脐橙**：是华盛顿脐橙的早熟芽变，于1978年引入中国。
+- **朋娜脐橙**：同样源自美国加利福尼亚州，也是华盛顿脐橙芽变选育的结果，同年（1978年）引入中国。
+### 2. 成熟期
+- **纽荷尔脐橙**：具体成熟时间未直接给出，但提到其为早熟品种。
+- **朋娜脐橙**：明确指出在赣南地区大约11月上中旬成熟，比纽荷尔略早。
+### 3. 树形与树势
+- **纽荷尔脐橙**：树势较强，树冠呈圆头形，叶片椭圆形且颜色深绿。
+- **朋娜脐橙**：树势中等，树冠紧凑呈圆头形，分枝较多，适合密植。
+### 4. 果实特征
+- **纽荷尔脐橙**：
+  - 果形：椭圆形
+  - 果色：橙红色
+  - 果肉：无核，汁多化渣，香味浓郁
+- **朋娜脐橙**：
+  - 果形：圆球形或椭圆形，果形端正
+  - 果色：橙黄至橙红，果皮较光滑
+  - 脐部：多为闭脐或微开脐
+  - 口感：肉质脆嫩化渣，风味浓甜，香气浓郁
+  - 单果重：约200～250g
+  - 可溶性固形物含量：12%～14%
+### 5. 抗逆性和管理
+- **纽荷尔脐橙**：资料中没有详细说明其抗病虫害能力或其他特殊管理需求。
+- **朋娜脐橙**：对溃疡病抗性一般，需要加强植保；如果管理不当容易出现大小年结果现象。
+### 6. 市场地位
+- **纽荷尔脐橙**：在中国脐橙栽培面积中占比超过85%，是最主要的栽培品种之一。
+- **朋娜脐橙**：虽然也受到市场欢迎，但其种植规模显然小于纽荷尔脐橙。
+综上所述，这两种脐橙虽然都属于优质早熟品种，但在起源、生长习性、果实特性以及市场需求等方面各有特点。希望这些信息能够帮助您更好地了解它们之间的差异。</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -2490,39 +2666,45 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>根据提供的参考资料，关于脐橙低温冻害的预防和救治措施如下：
+          <t>根据提供的参考资料，关于脐橙低温冻害的预防措施有较为详细的说明，但针对救治的具体方法资料中没有直接提及。因此，我将先列出已知的预防措施，并指出救治信息的缺失。
 ### 预防措施
-1. **树冠覆膜**：通过覆盖树冠来减少冷空气直接接触树木表面的机会。
-2. **树干刷白**：给树干涂上白色涂料（通常是石灰水），以反射阳光，减少昼夜温差对树体的影响。
-3. **喷施抗逆制剂**：使用能够提高植物抗寒性的化学或生物制剂进行叶面喷施。
-4. **采用喷灌防霜**：在预测到霜冻来临前夜，利用喷灌系统向果园内喷水形成一层冰壳保护果实免受更低温伤害。
-### 救治方法
-资料中未直接提及具体的冻害后救治措施。但基于预防原则及一般农业常识，可以采取以下步骤减轻已发生冻害的影响：
-- **及时修剪受损枝条**：去除明显受到冻害影响的部分，避免病菌侵入健康组织。
-- **加强营养管理**：适当增加肥料施用量，特别是磷钾肥，帮助恢复树势。
-- **保持土壤湿润**：合理灌溉，保证根系活力，促进植株恢复生长。
-- **注意病虫害防治**：冻害后的植株抵抗力较弱，更容易遭受病虫侵害，需加强监测并适时用药。
-请注意，上述建议中的救治方法并非直接来源于所提供的参考资料，而是基于通用农业实践提出的建议。对于具体操作，请结合实际情况并咨询专业人士。</t>
+1. **树冠覆膜**：通过覆盖树冠来减少冷空气直接接触树木的机会，从而减轻低温对脐橙的影响。
+2. **树干刷白**：给树干涂上白色涂料可以反射阳光，减少白天树干吸收过多热量导致夜间散热过快造成的温度骤降伤害。
+3. **喷施抗逆制剂**：使用能够提高植物抗寒能力的化学或生物制剂，增强脐橙树体自身的抵抗力。
+4. **采用喷灌防霜**：在预测到可能发生霜冻时，利用喷灌系统向果园内喷水形成一层保护膜，防止地表温度急剧下降。
+### 救治建议
+- 知识库中没有找到具体的救治方法。对于已经遭受冻害的脐橙树，通常需要采取一些恢复性措施如修剪受损枝条、加强肥水管理等来促进其恢复生长，但这部分内容并未在给出的参考资料里详细描述。
+综上所述，虽然我们了解了一些有效的预防策略，但对于如何处理已经发生的冻害情况，则需要参考更多专门针对灾后恢复的专业指导材料。</t>
         </is>
       </c>
       <c r="F21" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>根据提供的资料，脐橙低温冻害的预防和救治措施主要包括以下几个方面：
+          <t>脐橙低温冻害的预防和救治措施可以从以下几个方面进行：
 ### 预防措施
-1. **树盘覆盖**：在11月底进行树盘覆盖，使用杂草、稻草或绿肥等材料，厚度保持在15～20厘米之间。注意覆盖物距离主干至少10厘米以上。
-2. **树冠覆膜**：为树冠覆盖薄膜可以有效防止冷空气直接接触植株，减少热量散失。
-3. **树干刷白**：通过给树干涂上白色涂料（通常是石灰水），反射阳光，减少昼夜温差对树体的影响，从而减轻冻害。
-4. **喷施抗逆制剂**：提前喷施一些能够提高植物抗寒性的药剂或者营养液，增强脐橙树自身的耐寒能力。
-5. **采用喷灌防霜**：当预测到将有霜冻天气时，在夜间气温降至接近冰点之前开始喷水，利用水分结冰释放潜热来保护作物免受冻害。
+1. **树冠覆膜**：在寒冷季节来临前，对树冠进行覆盖保护，以减少冷空气直接接触果树。
+2. **树干刷白**：通过给树干涂上白色涂料（如石灰水），反射阳光，减少昼夜温差带来的伤害。
+3. **喷施抗逆制剂**：使用能够提高植物抗寒能力的药剂或肥料，增强脐橙树的耐寒性。
+4. **采用喷灌防霜**：利用喷灌系统，在霜冻即将发生时向果园内喷水，利用水结冰释放热量来防止温度过低。
+5. **合理布局园地**：选择适宜的海拔与坡位建园，避免在高寒地区盲目扩种。例如，晚熟脐橙（如伦晚）在三峡库区高海拔区域（&gt;350 m）应慎重推广。
 ### 救治措施
-资料中没有直接提到具体的冻害后救治方法。但是，一旦发生冻害，通常需要采取以下步骤：
-- **及时修剪受损枝条**：去除已经死亡或严重受损的部分，避免病菌侵入健康组织。
-- **加强管理**：包括合理施肥以促进恢复生长，以及密切监控并控制可能出现的次生病虫害问题。
-- **适当灌溉**：保持土壤适度湿润有助于树木恢复活力，但要避免积水造成根部腐烂。
-请注意，上述建议基于现有资料整理得出，对于具体操作细节可能还需参考更多专业指导或咨询农业专家。</t>
+根据冻害程度的不同，采取相应的处理方法：
+- **轻度冻害**：
+  - 摘除枯叶以减少水分消耗。
+  - 春季萌芽后剪除冻死的枯枝。
+  - 勤施薄施速效肥，并根外喷施0.2%～0.3%尿素+0.1%～0.3%磷酸二氢钾溶液促进恢复。
+- **中度冻害**：
+  - 剪除冻死的枯枝。
+  - 夏季修剪时调整骨干枝结构，疏去过多徒长枝。
+  - 适量结果以保持树势。
+- **重度冻害**：
+  - 截去冻死的部分。
+  - 对伤口进行涂蜡或用药保护，防止树脂病、裙腐病等感染。
+  - 待新芽萌发且死活界线明确后再进行修剪。
+  - 一般不留花或少留花，因为冻后树多畸形劣质花，坐果率低。
+以上措施可以帮助减轻低温冻害对脐橙的影响，并促进受损植株尽快恢复生长。</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
